--- a/Satélite Norte/.backup/SISGET - SISTEMA DE GERENCIAMENTO DE TRÁFEGO - Copia.xlsx
+++ b/Satélite Norte/.backup/SISGET - SISTEMA DE GERENCIAMENTO DE TRÁFEGO - Copia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tráfego Imp\OneDrive\Tráfego IMP\Ferramentas Gustavo\Sistema Auxiliar de Gerenciamento de Tráfego\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1763797ba848d3b0/Tráfego IMP/Ferramentas Gustavo/Soluções Excel/Satélite Norte/.backup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E1316F-158C-4D6B-91F4-89BB7C584A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E4E1316F-158C-4D6B-91F4-89BB7C584A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5EB13DC-3A3C-4F32-ADFB-902256C8B9A4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="587" firstSheet="4" activeTab="5" xr2:uid="{8804778D-2672-4FA4-985B-4CD56FF54310}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="587" firstSheet="3" activeTab="5" xr2:uid="{8804778D-2672-4FA4-985B-4CD56FF54310}"/>
   </bookViews>
   <sheets>
     <sheet name="PAINEL" sheetId="24" state="hidden" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="1598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="1604">
   <si>
     <t>HOJE ESTÁ TRANQUILO</t>
   </si>
@@ -4871,13 +4871,31 @@
     <t>JARDEL DE SOUSA OLIVEIRA - 5992</t>
   </si>
   <si>
-    <t>QUINTA</t>
-  </si>
-  <si>
-    <t>JOAO DE JESUS GOUVEIA - 6016</t>
-  </si>
-  <si>
     <t>EDIVALDO DE ARAUJO - 6217</t>
+  </si>
+  <si>
+    <t>SEXTA</t>
+  </si>
+  <si>
+    <t>( MOTORISTA DE GOIÂNIA )</t>
+  </si>
+  <si>
+    <t>IMPERATRIZ (MA) X VILA RICA (MT)</t>
+  </si>
+  <si>
+    <t>FERNANDO ALVES DE SOUZA - 6350</t>
+  </si>
+  <si>
+    <t>CARLOS ADRIANO DE SOUZA DO NASCIMENTO - 6222</t>
+  </si>
+  <si>
+    <t>JAKTAN DE OLIVEIRA RODRIGUES - 5836</t>
+  </si>
+  <si>
+    <t>ARIANO SILVA OLIVEIRA - 6349</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO OLIVEIRA SILVA NETO - 6378</t>
   </si>
 </sst>
 </file>
@@ -4887,7 +4905,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="40" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5174,6 +5192,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="23">
     <fill>
@@ -5304,7 +5329,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9BC2E6"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -5713,7 +5738,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="250">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6177,30 +6202,33 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6238,17 +6266,11 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6277,6 +6299,12 @@
     <xf numFmtId="14" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6284,87 +6312,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6385,10 +6332,37 @@
     <xf numFmtId="0" fontId="1" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6409,17 +6383,62 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="35" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6439,13 +6458,10 @@
     <xf numFmtId="0" fontId="35" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
@@ -9727,33 +9743,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="168"/>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
+      <c r="A1" s="166"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
     </row>
     <row r="2" spans="1:7" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
-      <c r="B2" s="168"/>
-      <c r="C2" s="168"/>
-      <c r="D2" s="168"/>
-      <c r="E2" s="168"/>
-      <c r="F2" s="168"/>
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="166"/>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
-      <c r="B3" s="169" t="str">
+      <c r="B3" s="168" t="str">
         <f ca="1">_xlfn.CONCAT("OLÁ ", 'BANCO DE DADOS'!I7,"!")</f>
         <v>OLÁ GUSTAVO!</v>
       </c>
-      <c r="C3" s="169"/>
-      <c r="D3" s="169"/>
-      <c r="E3" s="169"/>
-      <c r="F3" s="169"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9767,13 +9783,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="170" t="s">
+      <c r="B5" s="169" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="170"/>
-      <c r="F5" s="170"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="169"/>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="3" customHeight="1" x14ac:dyDescent="0.25">
@@ -9840,30 +9856,30 @@
     </row>
     <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
-      <c r="B12" s="166" t="s">
+      <c r="B12" s="171" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="166"/>
-      <c r="D12" s="166"/>
-      <c r="E12" s="165">
+      <c r="C12" s="171"/>
+      <c r="D12" s="171"/>
+      <c r="E12" s="170">
         <f>(COUNTIF('RESERVAS E QUARTOS'!C5:C9,"PNEU"))</f>
         <v>2</v>
       </c>
-      <c r="F12" s="165"/>
+      <c r="F12" s="170"/>
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="166" t="s">
+      <c r="B13" s="171" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="166"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="165">
+      <c r="C13" s="171"/>
+      <c r="D13" s="171"/>
+      <c r="E13" s="170">
         <f>COUNTIF('FROTA NOTURNA'!K3:K7,"NASCE NA GARAGEM")</f>
         <v>0</v>
       </c>
-      <c r="F13" s="165"/>
+      <c r="F13" s="170"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9895,6 +9911,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="B8:F8"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B9:F9"/>
@@ -9902,11 +9923,6 @@
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="B8:F8"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B7:F7" location="'ESCALA RODOVIÁRIA'!B2" display="&gt; ACESSAR ESCALA DE HOJE" xr:uid="{FC085309-8B37-4384-BC7A-942991620330}"/>
@@ -10089,7 +10105,7 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="120">
         <f>escala_do_fluxo[[#This Row],[DATA]]</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B2" s="12">
         <f>escala_do_fluxo[[#This Row],[HR. RD]]</f>
@@ -10098,7 +10114,7 @@
       <c r="C2" s="11"/>
       <c r="D2" s="11">
         <f>'ESCALA DO FLUXO'!D2</f>
-        <v>25011</v>
+        <v>25007</v>
       </c>
       <c r="E2" s="11" t="str" cm="1">
         <f t="array" ref="E2">IF(D2="CANCELADO","N/A",_xlfn.XLOOKUP(D2,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
@@ -10106,11 +10122,11 @@
       </c>
       <c r="F2" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I2,"-")),"CANCELADO")</f>
-        <v>JOSE ANTONIO INACIO VIEIRA</v>
+        <v>CLODOALDO PEREIRA DE LIMA</v>
       </c>
       <c r="G2" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I2,"-")),"CANCELADO")</f>
-        <v>5279</v>
+        <v>4067</v>
       </c>
       <c r="H2" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K2, " ",TEXT('ESCALA DO FLUXO'!F2,"HH:MM"))</f>
@@ -10120,7 +10136,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="120">
         <f>A2</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B3" s="12">
         <f>'ESCALA DO FLUXO'!F2</f>
@@ -10129,7 +10145,7 @@
       <c r="C3" s="11"/>
       <c r="D3" s="11">
         <f>'ESCALA DO FLUXO'!D2</f>
-        <v>25011</v>
+        <v>25007</v>
       </c>
       <c r="E3" s="11" t="str" cm="1">
         <f t="array" ref="E3">IF(D3="CANCELADO","N/A",_xlfn.XLOOKUP(D3,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
@@ -10137,11 +10153,11 @@
       </c>
       <c r="F3" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!J2,"-")),"CANCELADO")</f>
-        <v>MARCELO RIZO SANTANA</v>
+        <v>CANCELADO</v>
       </c>
       <c r="G3" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!J2,"-")),"CANCELADO")</f>
-        <v>2048</v>
+        <v>CANCELADO</v>
       </c>
       <c r="H3" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K2, " ",TEXT('ESCALA DO FLUXO'!F2,"HH:MM"))</f>
@@ -10163,7 +10179,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="120">
         <f t="shared" ref="A4:A12" si="0">A3</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B4" s="12">
         <f>'ESCALA DO FLUXO'!F3</f>
@@ -10172,19 +10188,19 @@
       <c r="C4" s="11"/>
       <c r="D4" s="11">
         <f>'ESCALA DO FLUXO'!D3</f>
-        <v>24001</v>
+        <v>25011</v>
       </c>
       <c r="E4" s="11" t="str" cm="1">
         <f t="array" ref="E4">IF(D4="CANCELADO","N/A",_xlfn.XLOOKUP(D4,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>SD02J77</v>
+        <v>OGT8A57</v>
       </c>
       <c r="F4" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I3,"-")),"CANCELADO")</f>
-        <v>VALDIR ALVES MIRANDA</v>
+        <v>MARCOS ATAIDE SILVA</v>
       </c>
       <c r="G4" s="127" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I3,"-")),"CANCELADO")</f>
-        <v>1364</v>
+        <v>1352</v>
       </c>
       <c r="H4" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K3, " ",TEXT('ESCALA DO FLUXO'!F3,"HH:MM"))</f>
@@ -10204,7 +10220,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B5" s="12">
         <f>'ESCALA DO FLUXO'!F3</f>
@@ -10213,19 +10229,19 @@
       <c r="C5" s="11"/>
       <c r="D5" s="11">
         <f>'ESCALA DO FLUXO'!D3</f>
-        <v>24001</v>
+        <v>25011</v>
       </c>
       <c r="E5" s="11" t="str" cm="1">
         <f t="array" ref="E5">IF(D5="CANCELADO","N/A",_xlfn.XLOOKUP(D5,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>SD02J77</v>
+        <v>OGT8A57</v>
       </c>
       <c r="F5" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!J3,"-")),"CANCELADO")</f>
-        <v>MANOEL SEVERINO DE SOUZA</v>
+        <v>FABIO MOREIRA DOS SANTOS</v>
       </c>
       <c r="G5" s="127" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!J3,"-")),"CANCELADO")</f>
-        <v>5200</v>
+        <v>3073</v>
       </c>
       <c r="H5" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K3, " ",TEXT('ESCALA DO FLUXO'!F3,"HH:MM"))</f>
@@ -10241,7 +10257,7 @@
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B6" s="12">
         <f>'ESCALA DO FLUXO'!F4</f>
@@ -10250,19 +10266,19 @@
       <c r="C6" s="11"/>
       <c r="D6" s="11">
         <f>'ESCALA DO FLUXO'!D4</f>
-        <v>19018</v>
+        <v>19005</v>
       </c>
       <c r="E6" s="11" t="str" cm="1">
         <f t="array" ref="E6">IF(D6="CANCELADO","N/A",_xlfn.XLOOKUP(D6,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTS0454</v>
+        <v>QTQ4724</v>
       </c>
       <c r="F6" s="126" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I4,"-")),"CANCELADO")</f>
-        <v>MARCUS AUGUSTO DE CARVALHO</v>
+        <v>JOSE CARLOS BEZERRA DA SILVA</v>
       </c>
       <c r="G6" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I4,"-")),"CANCELADO")</f>
-        <v>2398</v>
+        <v>3034</v>
       </c>
       <c r="H6" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K4, " ",TEXT('ESCALA DO FLUXO'!F4,"HH:MM"))</f>
@@ -10276,7 +10292,7 @@
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B7" s="12">
         <f>'ESCALA DO FLUXO'!F4</f>
@@ -10285,19 +10301,19 @@
       <c r="C7" s="11"/>
       <c r="D7" s="11">
         <f>'ESCALA DO FLUXO'!D4</f>
-        <v>19018</v>
+        <v>19005</v>
       </c>
       <c r="E7" s="11" t="str" cm="1">
         <f t="array" ref="E7">IF(D7="CANCELADO","N/A",_xlfn.XLOOKUP(D7,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTS0454</v>
+        <v>QTQ4724</v>
       </c>
       <c r="F7" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!J4,"-")),"CANCELADO")</f>
-        <v>LUIS CARLOS VIEIRA DE MELO SOUZA</v>
+        <v>CANCELADO</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!J4,"-")),"CANCELADO")</f>
-        <v>5535</v>
+        <v>CANCELADO</v>
       </c>
       <c r="H7" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K4, " ",TEXT('ESCALA DO FLUXO'!F4,"HH:MM"))</f>
@@ -10307,7 +10323,7 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B8" s="12">
         <f>'ESCALA DO FLUXO'!F5</f>
@@ -10332,13 +10348,13 @@
       </c>
       <c r="H8" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K5, " ",TEXT('ESCALA DO FLUXO'!F5,"HH:MM"))</f>
-        <v xml:space="preserve"> 10:00</v>
+        <v>IMPERATRIZ (MA) X VILA RICA (MT) 10:00</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B9" s="12">
         <f>escala_do_fluxo[[#This Row],[HR. RD]]</f>
@@ -10363,13 +10379,13 @@
       </c>
       <c r="H9" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K5, " ",TEXT('ESCALA DO FLUXO'!F5,"HH:MM"))</f>
-        <v xml:space="preserve"> 10:00</v>
+        <v>IMPERATRIZ (MA) X VILA RICA (MT) 10:00</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B10" s="12">
         <f>'ESCALA DO FLUXO'!F7</f>
@@ -10378,19 +10394,19 @@
       <c r="C10" s="11"/>
       <c r="D10" s="11">
         <f>'ESCALA DO FLUXO'!D7</f>
-        <v>19023</v>
+        <v>19021</v>
       </c>
       <c r="E10" s="11" t="str" cm="1">
         <f t="array" ref="E10">IF(D10="CANCELADO","N/A",_xlfn.XLOOKUP(D10,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTP1I89</v>
+        <v>QTR5657</v>
       </c>
       <c r="F10" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I7,"-")),"CANCELADO")</f>
-        <v>JOAO DE JESUS GOUVEIA</v>
+        <v>FERNANDO ALVES DE SOUZA</v>
       </c>
       <c r="G10" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I7,"-")),"CANCELADO")</f>
-        <v>6016</v>
+        <v>6350</v>
       </c>
       <c r="H10" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K7, " ",TEXT('ESCALA DO FLUXO'!F7,"HH:MM"))</f>
@@ -10400,7 +10416,7 @@
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B11" s="12">
         <f>'ESCALA DO FLUXO'!F7</f>
@@ -10409,19 +10425,19 @@
       <c r="C11" s="11"/>
       <c r="D11" s="11">
         <f>'ESCALA DO FLUXO'!D7</f>
-        <v>19023</v>
+        <v>19021</v>
       </c>
       <c r="E11" s="11" t="str" cm="1">
         <f t="array" ref="E11">IF(D11="CANCELADO","N/A",_xlfn.XLOOKUP(D11,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTP1I89</v>
+        <v>QTR5657</v>
       </c>
       <c r="F11" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!J7,"-")),"CANCELADO")</f>
-        <v>CLODOALDO PEREIRA DE LIMA</v>
+        <v>AELSON PEREIRA DO NASCIMENTO</v>
       </c>
       <c r="G11" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!J7,"-")),"CANCELADO")</f>
-        <v>4067</v>
+        <v>5682</v>
       </c>
       <c r="H11" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K7, " ",TEXT('ESCALA DO FLUXO'!F7,"HH:MM"))</f>
@@ -10431,7 +10447,7 @@
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B12" s="12">
         <f>'ESCALA DO FLUXO'!F6</f>
@@ -10440,19 +10456,19 @@
       <c r="C12" s="11"/>
       <c r="D12" s="11">
         <f>'ESCALA DO FLUXO'!D6</f>
-        <v>19003</v>
+        <v>19007</v>
       </c>
       <c r="E12" s="11" t="str" cm="1">
         <f t="array" ref="E12">IF(D12="CANCELADO","N/A",_xlfn.XLOOKUP(D12,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTQ8294</v>
+        <v>QTP0317</v>
       </c>
       <c r="F12" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I6,"-")),"CANCELADO")</f>
-        <v>RONNE RODRIGUES DE SOUSA</v>
+        <v>EDUARDO SANTOS BEZERRA</v>
       </c>
       <c r="G12" s="127" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I6,"-")),"CANCELADO")</f>
-        <v>5025</v>
+        <v>4066</v>
       </c>
       <c r="H12" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K6, " ",TEXT('ESCALA DO FLUXO'!F6,"HH:MM"))</f>
@@ -10462,7 +10478,7 @@
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="120">
         <f>A12</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B13" s="132">
         <f>'ESCALA DO FLUXO'!F16</f>
@@ -10471,19 +10487,19 @@
       <c r="C13" s="133"/>
       <c r="D13" s="11">
         <f>'ESCALA DO FLUXO'!D16</f>
-        <v>19013</v>
+        <v>19024</v>
       </c>
       <c r="E13" s="11" t="str" cm="1">
         <f t="array" ref="E13">IF(D13="CANCELADO","N/A",_xlfn.XLOOKUP(D13,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTR8894</v>
+        <v>QTP1769</v>
       </c>
       <c r="F13" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I16,"-")),"CANCELADO")</f>
-        <v>KLEBER OLIVEIRA LIMA</v>
+        <v>FRANCISCO BATISTA DE LIMA</v>
       </c>
       <c r="G13" s="127" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I16,"-")),"CANCELADO")</f>
-        <v>5849</v>
+        <v>1827</v>
       </c>
       <c r="H13" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K16, " ",TEXT('ESCALA DO FLUXO'!F16,"HH:MM"))</f>
@@ -10493,7 +10509,7 @@
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="144">
         <f>A13</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B14" s="145" t="e">
         <f>'ESCALA DO FLUXO'!#REF!</f>
@@ -10520,7 +10536,7 @@
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="144">
         <f>A14</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B15" s="145" t="e">
         <f>'ESCALA DO FLUXO'!#REF!</f>
@@ -10653,28 +10669,28 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="120">
         <f>escala_do_fluxo[[#This Row],[DATA]]</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B2" s="12">
         <f>'ESCALA DO FLUXO'!F17</f>
         <v>0.8125</v>
       </c>
       <c r="C2" s="11"/>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="11">
         <f>'ESCALA DO FLUXO'!D17</f>
-        <v>CANCELADO</v>
+        <v>18016</v>
       </c>
       <c r="E2" s="11" t="str" cm="1">
         <f t="array" ref="E2">IF(D2="CANCELADO","N/A",_xlfn.XLOOKUP(D2,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>N/A</v>
+        <v>PRK6658</v>
       </c>
       <c r="F2" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I17,"-")),"CANCELADO")</f>
-        <v>CANCELADO</v>
+        <v>REGINALDO DE SOUSA OLIVEIRA</v>
       </c>
       <c r="G2" s="127" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I17,"-")),"CANCELADO")</f>
-        <v>CANCELADO</v>
+        <v>5412</v>
       </c>
       <c r="H2" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K17, " ",TEXT('ESCALA DO FLUXO'!F17,"HH:MM"))</f>
@@ -10696,7 +10712,7 @@
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="120">
         <f>A2</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B3" s="12">
         <f>'ESCALA DO FLUXO'!F19</f>
@@ -10705,19 +10721,19 @@
       <c r="C3" s="11"/>
       <c r="D3" s="11">
         <f>'ESCALA DO FLUXO'!D19</f>
-        <v>15600</v>
+        <v>19015</v>
       </c>
       <c r="E3" s="11" t="str" cm="1">
         <f t="array" ref="E3">IF(D3="CANCELADO","N/A",_xlfn.XLOOKUP(D3,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>OOC4709</v>
+        <v>QTS1804</v>
       </c>
       <c r="F3" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I19,"-")),"CANCELADO")</f>
-        <v>JERZUALDO DA SILVA GOMES</v>
+        <v>FRANCISCO ALVES DA PAZ JUNIOR</v>
       </c>
       <c r="G3" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I19,"-")),"CANCELADO")</f>
-        <v>4077</v>
+        <v>1247</v>
       </c>
       <c r="H3" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K19, " ",TEXT('ESCALA DO FLUXO'!F19,"HH:MM"))</f>
@@ -10727,7 +10743,7 @@
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="120">
         <f t="shared" ref="A4:A14" si="0">A3</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B4" s="12">
         <f>'ESCALA DO FLUXO'!F15</f>
@@ -10736,19 +10752,19 @@
       <c r="C4" s="11"/>
       <c r="D4" s="11">
         <f>'ESCALA DO FLUXO'!D15</f>
-        <v>24005</v>
+        <v>25012</v>
       </c>
       <c r="E4" s="11" t="str" cm="1">
         <f t="array" ref="E4">IF(D4="CANCELADO","N/A",_xlfn.XLOOKUP(D4,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>SDN7G87</v>
+        <v>OGT8A57</v>
       </c>
       <c r="F4" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I15,"-")),"CANCELADO")</f>
-        <v>FRANCISCO BATISTA DE LIMA</v>
+        <v>BRUNO MATOS DA ROCHA</v>
       </c>
       <c r="G4" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I15,"-")),"CANCELADO")</f>
-        <v>1827</v>
+        <v>6013</v>
       </c>
       <c r="H4" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K15, " ",TEXT('ESCALA DO FLUXO'!F15,"HH:MM"))</f>
@@ -10768,7 +10784,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B5" s="12">
         <f>'ESCALA DO FLUXO'!F15</f>
@@ -10777,19 +10793,19 @@
       <c r="C5" s="11"/>
       <c r="D5" s="11">
         <f>'ESCALA DO FLUXO'!D15</f>
-        <v>24005</v>
+        <v>25012</v>
       </c>
       <c r="E5" s="11" t="str" cm="1">
         <f t="array" ref="E5">IF(D5="CANCELADO","N/A",_xlfn.XLOOKUP(D5,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>SDN7G87</v>
+        <v>OGT8A57</v>
       </c>
       <c r="F5" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!J15,"-")),"CANCELADO")</f>
-        <v>ADEMILTON DE OLIVEIRA SILVA</v>
+        <v>ANTONIO FRANCINALDO DE OLIVEIRA MARQUES</v>
       </c>
       <c r="G5" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!J15,"-")),"CANCELADO")</f>
-        <v>5559</v>
+        <v>5018</v>
       </c>
       <c r="H5" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K15, " ",TEXT('ESCALA DO FLUXO'!F15,"HH:MM"))</f>
@@ -10805,28 +10821,28 @@
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B6" s="12">
         <f>'ESCALA DO FLUXO'!F20</f>
         <v>0.84166666666666667</v>
       </c>
       <c r="C6" s="11"/>
-      <c r="D6" s="11">
+      <c r="D6" s="11" t="str">
         <f>'ESCALA DO FLUXO'!D20</f>
-        <v>19006</v>
+        <v>CANCELADO</v>
       </c>
       <c r="E6" s="11" t="str" cm="1">
         <f t="array" ref="E6">IF(D6="CANCELADO","N/A",_xlfn.XLOOKUP(D6,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTO8637</v>
+        <v>N/A</v>
       </c>
       <c r="F6" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I20,"-")),"CANCELADO")</f>
-        <v>MARCIO DE SOUSA MATOS</v>
+        <v>CANCELADO</v>
       </c>
       <c r="G6" s="127" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I20,"-")),"CANCELADO")</f>
-        <v>5264</v>
+        <v>CANCELADO</v>
       </c>
       <c r="H6" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K20, " ",TEXT('ESCALA DO FLUXO'!F20,"HH:MM"))</f>
@@ -10836,28 +10852,28 @@
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B7" s="12">
         <f>'ESCALA DO FLUXO'!F20</f>
         <v>0.84166666666666667</v>
       </c>
       <c r="C7" s="11"/>
-      <c r="D7" s="11">
+      <c r="D7" s="11" t="str">
         <f>'ESCALA DO FLUXO'!D20</f>
-        <v>19006</v>
+        <v>CANCELADO</v>
       </c>
       <c r="E7" s="11" t="str" cm="1">
         <f t="array" ref="E7">IF(D7="CANCELADO","N/A",_xlfn.XLOOKUP(D7,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTO8637</v>
+        <v>N/A</v>
       </c>
       <c r="F7" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!J20,"-")),"CANCELADO")</f>
-        <v>NILSON CORTEZ MIRANDA</v>
+        <v>CANCELADO</v>
       </c>
       <c r="G7" s="127" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!J20,"-")),"CANCELADO")</f>
-        <v>5636</v>
+        <v>CANCELADO</v>
       </c>
       <c r="H7" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K20, " ",TEXT('ESCALA DO FLUXO'!F20,"HH:MM"))</f>
@@ -10867,7 +10883,7 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B8" s="12">
         <f>'ESCALA DO FLUXO'!F18</f>
@@ -10876,19 +10892,19 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11">
         <f>'ESCALA DO FLUXO'!D18</f>
-        <v>24004</v>
+        <v>25008</v>
       </c>
       <c r="E8" s="11" t="str" cm="1">
         <f t="array" ref="E8">IF(D8="CANCELADO","N/A",_xlfn.XLOOKUP(D8,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>SDJ8I27</v>
+        <v>OGT8A57</v>
       </c>
       <c r="F8" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I18,"-")),"CANCELADO")</f>
-        <v>ANTONIO MARQUES NETO DOS SANTOS</v>
+        <v>JARDEL DE SOUSA OLIVEIRA</v>
       </c>
       <c r="G8" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I18,"-")),"CANCELADO")</f>
-        <v>1738</v>
+        <v>5992</v>
       </c>
       <c r="H8" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K18, " ",TEXT('ESCALA DO FLUXO'!F18,"HH:MM"))</f>
@@ -10898,7 +10914,7 @@
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B9" s="12">
         <f>'ESCALA DO FLUXO'!F21</f>
@@ -10907,19 +10923,19 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11">
         <f>'ESCALA DO FLUXO'!D21</f>
-        <v>19008</v>
+        <v>19014</v>
       </c>
       <c r="E9" s="11" t="str" cm="1">
         <f t="array" ref="E9">IF(D9="CANCELADO","N/A",_xlfn.XLOOKUP(D9,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTS0484</v>
+        <v>QTS1814</v>
       </c>
       <c r="F9" s="126" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I21,"-")),"CANCELADO")</f>
-        <v>MERVAL DE SOUSA</v>
+        <v>KLEBER OLIVEIRA LIMA</v>
       </c>
       <c r="G9" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I21,"-")),"CANCELADO")</f>
-        <v>2880</v>
+        <v>5849</v>
       </c>
       <c r="H9" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K21, " ",TEXT('ESCALA DO FLUXO'!F21,"HH:MM"))</f>
@@ -10929,7 +10945,7 @@
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B10" s="12">
         <f>'ESCALA DO FLUXO'!F21</f>
@@ -10938,19 +10954,19 @@
       <c r="C10" s="11"/>
       <c r="D10" s="11">
         <f>'ESCALA DO FLUXO'!D21</f>
-        <v>19008</v>
+        <v>19014</v>
       </c>
       <c r="E10" s="11" t="str" cm="1">
         <f t="array" ref="E10">IF(D10="CANCELADO","N/A",_xlfn.XLOOKUP(D10,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTS0484</v>
+        <v>QTS1814</v>
       </c>
       <c r="F10" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!J21,"-")),"CANCELADO")</f>
-        <v>JOSE ALVES DE FREITAS NETO</v>
+        <v>CANCELADO</v>
       </c>
       <c r="G10" s="127" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!J21,"-")),"CANCELADO")</f>
-        <v>5027</v>
+        <v>CANCELADO</v>
       </c>
       <c r="H10" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K21, " ",TEXT('ESCALA DO FLUXO'!F21,"HH:MM"))</f>
@@ -10960,7 +10976,7 @@
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B11" s="12">
         <f>'ESCALA DO FLUXO'!F22</f>
@@ -10969,19 +10985,19 @@
       <c r="C11" s="11"/>
       <c r="D11" s="11">
         <f>'ESCALA DO FLUXO'!D22</f>
-        <v>19016</v>
+        <v>19010</v>
       </c>
       <c r="E11" s="11" t="str" cm="1">
         <f t="array" ref="E11">IF(D11="CANCELADO","N/A",_xlfn.XLOOKUP(D11,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTS0D94</v>
+        <v>QTO8077</v>
       </c>
       <c r="F11" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!I22,"-")),"CANCELADO")</f>
-        <v>RAFAEL JOSE TOME DE LIMA</v>
+        <v>MARCIO DE SOUSA MATOS</v>
       </c>
       <c r="G11" s="127" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!I22,"-")),"CANCELADO")</f>
-        <v>5537</v>
+        <v>5264</v>
       </c>
       <c r="H11" s="121" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K22, " ",TEXT('ESCALA DO FLUXO'!F22,"HH:MM"))</f>
@@ -10991,7 +11007,7 @@
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B12" s="140">
         <f>'ESCALA DO FLUXO'!F22</f>
@@ -11000,19 +11016,19 @@
       <c r="C12" s="141"/>
       <c r="D12" s="141">
         <f>'ESCALA DO FLUXO'!D22</f>
-        <v>19016</v>
+        <v>19010</v>
       </c>
       <c r="E12" s="141" t="str" cm="1">
         <f t="array" ref="E12">IF(D12="CANCELADO","N/A",_xlfn.XLOOKUP(D12,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTS0D94</v>
+        <v>QTO8077</v>
       </c>
       <c r="F12" s="140" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA DO FLUXO'!J22,"-")),"CANCELADO")</f>
-        <v>JOAO DA SILVA MORAIS</v>
+        <v>ANDSON WAGNER NASCIMENTO SOUZA</v>
       </c>
       <c r="G12" s="140" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA DO FLUXO'!J22,"-")),"CANCELADO")</f>
-        <v>2978</v>
+        <v>2902</v>
       </c>
       <c r="H12" s="142" t="str">
         <f>_xlfn.CONCAT('ESCALA DO FLUXO'!K22, " ",TEXT('ESCALA DO FLUXO'!F22,"HH:MM"))</f>
@@ -11022,7 +11038,7 @@
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B13" s="140">
         <f>'ESCALA DO FLUXO'!F23</f>
@@ -11052,7 +11068,7 @@
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="120">
         <f t="shared" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B14" s="140">
         <v>0.85763888888888884</v>
@@ -11326,7 +11342,7 @@
       </c>
       <c r="I5" s="25" t="str">
         <f ca="1">TEXT(NOW(),"DD/MM/AA")</f>
-        <v>28/08/25</v>
+        <v>20/03/26</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -19166,26 +19182,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="6:14" s="72" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G1" s="172" t="s">
+      <c r="G1" s="173" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="173"/>
     </row>
     <row r="2" spans="6:14" x14ac:dyDescent="0.25">
-      <c r="G2" s="173" t="s">
+      <c r="G2" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="173"/>
-      <c r="K2" s="173"/>
-      <c r="L2" s="173"/>
-      <c r="M2" s="173"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
+      <c r="L2" s="174"/>
+      <c r="M2" s="174"/>
     </row>
     <row r="5" spans="6:14" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="6:14" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19256,65 +19272,65 @@
     <row r="23" spans="4:19" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="4:19" ht="11.45" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="G25" s="173" t="s">
+      <c r="G25" s="174" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="173"/>
-      <c r="I25" s="173"/>
-      <c r="J25" s="173"/>
-      <c r="K25" s="173"/>
-      <c r="L25" s="173"/>
-      <c r="M25" s="173"/>
+      <c r="H25" s="174"/>
+      <c r="I25" s="174"/>
+      <c r="J25" s="174"/>
+      <c r="K25" s="174"/>
+      <c r="L25" s="174"/>
+      <c r="M25" s="174"/>
     </row>
     <row r="26" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D26" s="70"/>
-      <c r="E26" s="171" t="s">
+      <c r="E26" s="172" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="171"/>
-      <c r="G26" s="171"/>
-      <c r="H26" s="171"/>
-      <c r="I26" s="171"/>
-      <c r="J26" s="171"/>
-      <c r="K26" s="171"/>
-      <c r="L26" s="171"/>
-      <c r="M26" s="171"/>
-      <c r="N26" s="171"/>
-      <c r="O26" s="171"/>
+      <c r="F26" s="172"/>
+      <c r="G26" s="172"/>
+      <c r="H26" s="172"/>
+      <c r="I26" s="172"/>
+      <c r="J26" s="172"/>
+      <c r="K26" s="172"/>
+      <c r="L26" s="172"/>
+      <c r="M26" s="172"/>
+      <c r="N26" s="172"/>
+      <c r="O26" s="172"/>
       <c r="P26" s="70"/>
     </row>
     <row r="27" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D27" s="171" t="s">
+      <c r="D27" s="172" t="s">
         <v>21</v>
       </c>
-      <c r="E27" s="171"/>
-      <c r="F27" s="171"/>
-      <c r="G27" s="171"/>
-      <c r="H27" s="171"/>
-      <c r="I27" s="171"/>
-      <c r="J27" s="171"/>
-      <c r="K27" s="171"/>
-      <c r="L27" s="171"/>
-      <c r="M27" s="171"/>
-      <c r="N27" s="171"/>
-      <c r="O27" s="171"/>
-      <c r="P27" s="171"/>
+      <c r="E27" s="172"/>
+      <c r="F27" s="172"/>
+      <c r="G27" s="172"/>
+      <c r="H27" s="172"/>
+      <c r="I27" s="172"/>
+      <c r="J27" s="172"/>
+      <c r="K27" s="172"/>
+      <c r="L27" s="172"/>
+      <c r="M27" s="172"/>
+      <c r="N27" s="172"/>
+      <c r="O27" s="172"/>
+      <c r="P27" s="172"/>
     </row>
     <row r="28" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D28" s="71"/>
-      <c r="E28" s="171" t="s">
+      <c r="E28" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="171"/>
-      <c r="G28" s="171"/>
-      <c r="H28" s="171"/>
-      <c r="I28" s="171"/>
-      <c r="J28" s="171"/>
-      <c r="K28" s="171"/>
-      <c r="L28" s="171"/>
-      <c r="M28" s="171"/>
-      <c r="N28" s="171"/>
-      <c r="O28" s="171"/>
+      <c r="F28" s="172"/>
+      <c r="G28" s="172"/>
+      <c r="H28" s="172"/>
+      <c r="I28" s="172"/>
+      <c r="J28" s="172"/>
+      <c r="K28" s="172"/>
+      <c r="L28" s="172"/>
+      <c r="M28" s="172"/>
+      <c r="N28" s="172"/>
+      <c r="O28" s="172"/>
       <c r="P28" s="71"/>
       <c r="S28" s="74" t="s">
         <v>23</v>
@@ -19380,20 +19396,20 @@
     </row>
     <row r="3" spans="1:12" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="175" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="174"/>
-      <c r="D3" s="174"/>
-      <c r="E3" s="174"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="175" t="str">
+      <c r="G3" s="176" t="str">
         <f ca="1">_xlfn.CONCAT("atualizado em: ",TEXT(NOW(),"DD/MM/AA - HH:MM")," (",'BANCO DE DADOS'!I7,")")</f>
-        <v>atualizado em: 28/08/25 - 18:49 (GUSTAVO)</v>
-      </c>
-      <c r="H3" s="176"/>
-      <c r="I3" s="176"/>
-      <c r="J3" s="176"/>
+        <v>atualizado em: 20/03/26 - 05:36 (GUSTAVO)</v>
+      </c>
+      <c r="H3" s="177"/>
+      <c r="I3" s="177"/>
+      <c r="J3" s="177"/>
       <c r="K3" s="48" t="s">
         <v>25</v>
       </c>
@@ -19436,13 +19452,13 @@
         <v>32</v>
       </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="177" t="s">
+      <c r="G5" s="178" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="178"/>
-      <c r="I5" s="178"/>
-      <c r="J5" s="178"/>
-      <c r="K5" s="179"/>
+      <c r="H5" s="179"/>
+      <c r="I5" s="179"/>
+      <c r="J5" s="179"/>
+      <c r="K5" s="180"/>
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -19772,13 +19788,13 @@
   <sheetData>
     <row r="1" spans="4:31" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D2" s="180" t="s">
+      <c r="D2" s="181" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="181"/>
-      <c r="F2" s="181"/>
-      <c r="G2" s="181"/>
-      <c r="H2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="182"/>
+      <c r="H2" s="183"/>
       <c r="I2" s="106"/>
       <c r="J2" s="106"/>
       <c r="K2" s="106"/>
@@ -19862,11 +19878,11 @@
     <row r="4" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D4" s="107">
         <f ca="1">TODAY()</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="E4" s="108">
         <f>'ESCALA DO FLUXO'!D2</f>
-        <v>25011</v>
+        <v>25007</v>
       </c>
       <c r="F4" s="21">
         <v>0.3</v>
@@ -19882,11 +19898,11 @@
       <c r="K4" s="108"/>
       <c r="N4" s="107">
         <f ca="1">D4</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="O4" s="108">
         <f>'ESCALA DO FLUXO'!D7</f>
-        <v>19023</v>
+        <v>19021</v>
       </c>
       <c r="P4" s="21">
         <v>0.39583333333333331</v>
@@ -19902,11 +19918,11 @@
       <c r="U4" s="108"/>
       <c r="X4" s="107">
         <f ca="1">D4</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="Y4" s="108">
         <f>'ESCALA DO FLUXO'!D16</f>
-        <v>19013</v>
+        <v>19024</v>
       </c>
       <c r="Z4" s="21">
         <v>0.47013888888888888</v>
@@ -19924,11 +19940,11 @@
     <row r="5" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="107">
         <f ca="1">D4</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="E5" s="108">
         <f>'ESCALA DO FLUXO'!D3</f>
-        <v>24001</v>
+        <v>25011</v>
       </c>
       <c r="F5" s="21">
         <v>0.33333333333333331</v>
@@ -19944,11 +19960,11 @@
       <c r="K5" s="108"/>
       <c r="N5" s="107">
         <f ca="1">N4</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="O5" s="108">
         <f>'ESCALA DO FLUXO'!D15</f>
-        <v>24005</v>
+        <v>25012</v>
       </c>
       <c r="P5" s="21">
         <v>0.82777777777777772</v>
@@ -19964,11 +19980,11 @@
       <c r="U5" s="108"/>
       <c r="X5" s="107">
         <f ca="1">X4</f>
-        <v>45897</v>
-      </c>
-      <c r="Y5" s="108" t="str">
+        <v>46101</v>
+      </c>
+      <c r="Y5" s="108">
         <f>'ESCALA DO FLUXO'!D17</f>
-        <v>CANCELADO</v>
+        <v>18016</v>
       </c>
       <c r="Z5" s="21">
         <v>0.8125</v>
@@ -19986,11 +20002,11 @@
     <row r="6" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="107">
         <f ca="1">D10</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="E6" s="108">
         <f>'ESCALA DO FLUXO'!D4</f>
-        <v>19018</v>
+        <v>19005</v>
       </c>
       <c r="F6" s="21">
         <v>0.39583333333333331</v>
@@ -20006,11 +20022,11 @@
       <c r="K6" s="108"/>
       <c r="N6" s="107">
         <f t="shared" ref="N6:N12" ca="1" si="0">N5</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="O6" s="108">
         <f>'ESCALA DO FLUXO'!D9</f>
-        <v>19016</v>
+        <v>19010</v>
       </c>
       <c r="P6" s="21">
         <v>0.35416666666666669</v>
@@ -20026,11 +20042,11 @@
       <c r="U6" s="108"/>
       <c r="X6" s="107">
         <f ca="1">X5</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="Y6" s="108">
         <f>'ESCALA DO FLUXO'!D18</f>
-        <v>24004</v>
+        <v>25008</v>
       </c>
       <c r="Z6" s="21">
         <v>0.84375</v>
@@ -20048,11 +20064,11 @@
     <row r="7" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D7" s="107">
         <f ca="1">D5</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="E7" s="108">
         <f>'ESCALA DO FLUXO'!D6</f>
-        <v>19003</v>
+        <v>19007</v>
       </c>
       <c r="F7" s="21">
         <v>0.39583333333333331</v>
@@ -20068,11 +20084,11 @@
       <c r="K7" s="108"/>
       <c r="N7" s="107">
         <f t="shared" ca="1" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="O7" s="108">
         <f>'ESCALA DO FLUXO'!D14</f>
-        <v>24003</v>
+        <v>24014</v>
       </c>
       <c r="P7" s="21">
         <v>0.79166666666666663</v>
@@ -20088,11 +20104,11 @@
       <c r="U7" s="108"/>
       <c r="X7" s="107">
         <f t="shared" ref="X7:X12" ca="1" si="1">X6</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="Y7" s="108">
         <f>'ESCALA DO FLUXO'!D10</f>
-        <v>19006</v>
+        <v>20015</v>
       </c>
       <c r="Z7" s="21">
         <v>0.29166666666666669</v>
@@ -20110,11 +20126,11 @@
     <row r="8" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D8" s="107">
         <f t="shared" ref="D8:D11" ca="1" si="2">D7</f>
-        <v>45897</v>
-      </c>
-      <c r="E8" s="108">
+        <v>46101</v>
+      </c>
+      <c r="E8" s="108" t="str">
         <f>'ESCALA DO FLUXO'!D20</f>
-        <v>19006</v>
+        <v>CANCELADO</v>
       </c>
       <c r="F8" s="21">
         <v>0.84166666666666667</v>
@@ -20130,7 +20146,7 @@
       <c r="K8" s="108"/>
       <c r="N8" s="107">
         <f t="shared" ca="1" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="O8" s="108"/>
       <c r="P8" s="21"/>
@@ -20141,11 +20157,11 @@
       <c r="U8" s="108"/>
       <c r="X8" s="107">
         <f t="shared" ca="1" si="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="Y8" s="108">
         <f>'ESCALA DO FLUXO'!D11</f>
-        <v>25006</v>
+        <v>25005</v>
       </c>
       <c r="Z8" s="21">
         <v>0.79166666666666663</v>
@@ -20163,11 +20179,11 @@
     <row r="9" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D9" s="107">
         <f t="shared" ca="1" si="2"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="E9" s="108">
         <f>'ESCALA DO FLUXO'!D21</f>
-        <v>19008</v>
+        <v>19014</v>
       </c>
       <c r="F9" s="21">
         <v>0.85416666666666663</v>
@@ -20183,7 +20199,7 @@
       <c r="K9" s="108"/>
       <c r="N9" s="107">
         <f t="shared" ca="1" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="O9" s="108"/>
       <c r="P9" s="108"/>
@@ -20194,7 +20210,7 @@
       <c r="U9" s="108"/>
       <c r="X9" s="107">
         <f t="shared" ca="1" si="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="Y9" s="108" t="str">
         <f>'ESCALA DO FLUXO'!D12</f>
@@ -20216,11 +20232,11 @@
     <row r="10" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D10" s="107">
         <f t="shared" ca="1" si="2"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="E10" s="108">
         <f>'ESCALA DO FLUXO'!D22</f>
-        <v>19016</v>
+        <v>19010</v>
       </c>
       <c r="F10" s="21">
         <v>0.87847222222222221</v>
@@ -20236,7 +20252,7 @@
       <c r="K10" s="108"/>
       <c r="N10" s="107">
         <f t="shared" ca="1" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="O10" s="108"/>
       <c r="P10" s="108"/>
@@ -20247,7 +20263,7 @@
       <c r="U10" s="108"/>
       <c r="X10" s="107">
         <f t="shared" ca="1" si="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="Y10" s="108"/>
       <c r="Z10" s="108"/>
@@ -20260,11 +20276,11 @@
     <row r="11" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D11" s="107">
         <f t="shared" ca="1" si="2"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="E11" s="108">
         <f>'ESCALA DO FLUXO'!D19</f>
-        <v>15600</v>
+        <v>19015</v>
       </c>
       <c r="F11" s="21">
         <v>0.79166666666666663</v>
@@ -20280,7 +20296,7 @@
       <c r="K11" s="108"/>
       <c r="N11" s="107">
         <f t="shared" ca="1" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="O11" s="108"/>
       <c r="P11" s="108"/>
@@ -20291,7 +20307,7 @@
       <c r="U11" s="108"/>
       <c r="X11" s="107">
         <f t="shared" ca="1" si="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="Y11" s="108"/>
       <c r="Z11" s="108"/>
@@ -20304,7 +20320,7 @@
     <row r="12" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="107">
         <f t="shared" ref="D12" ca="1" si="3">D11</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="E12" s="108" t="str">
         <f>'ESCALA RODOVIÁRIA'!G57</f>
@@ -20325,7 +20341,7 @@
       <c r="K12" s="108"/>
       <c r="N12" s="107">
         <f t="shared" ca="1" si="0"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="O12" s="108"/>
       <c r="P12" s="108"/>
@@ -20336,7 +20352,7 @@
       <c r="U12" s="108"/>
       <c r="X12" s="107">
         <f t="shared" ca="1" si="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="Y12" s="108"/>
       <c r="Z12" s="37"/>
@@ -20347,13 +20363,13 @@
       <c r="AE12" s="108"/>
     </row>
     <row r="13" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D13" s="180" t="s">
+      <c r="D13" s="181" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="181"/>
-      <c r="F13" s="181"/>
-      <c r="G13" s="181"/>
-      <c r="H13" s="181"/>
+      <c r="E13" s="182"/>
+      <c r="F13" s="182"/>
+      <c r="G13" s="182"/>
+      <c r="H13" s="182"/>
       <c r="I13" s="105"/>
       <c r="J13" s="106"/>
       <c r="K13" s="106"/>
@@ -20367,22 +20383,22 @@
       <c r="S13" s="185"/>
       <c r="T13" s="185"/>
       <c r="U13" s="185"/>
-      <c r="X13" s="180" t="s">
+      <c r="X13" s="181" t="s">
         <v>66</v>
       </c>
-      <c r="Y13" s="181"/>
-      <c r="Z13" s="181"/>
-      <c r="AA13" s="181"/>
-      <c r="AB13" s="182"/>
+      <c r="Y13" s="182"/>
+      <c r="Z13" s="182"/>
+      <c r="AA13" s="182"/>
+      <c r="AB13" s="183"/>
       <c r="AC13" s="106"/>
       <c r="AD13" s="106"/>
       <c r="AE13" s="106"/>
     </row>
     <row r="14" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D14" s="187" t="s">
+      <c r="D14" s="186" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="188"/>
+      <c r="E14" s="187"/>
       <c r="F14" s="108">
         <v>19002</v>
       </c>
@@ -20393,20 +20409,20 @@
       <c r="I14" s="108"/>
       <c r="J14" s="108"/>
       <c r="K14" s="108"/>
-      <c r="N14" s="189" t="s">
+      <c r="N14" s="188" t="s">
         <v>67</v>
       </c>
-      <c r="O14" s="189"/>
+      <c r="O14" s="188"/>
       <c r="P14" s="108"/>
       <c r="Q14" s="108"/>
       <c r="R14" s="108"/>
       <c r="S14" s="108"/>
       <c r="T14" s="108"/>
       <c r="U14" s="108"/>
-      <c r="X14" s="189" t="s">
+      <c r="X14" s="188" t="s">
         <v>67</v>
       </c>
-      <c r="Y14" s="189"/>
+      <c r="Y14" s="188"/>
       <c r="Z14" s="108"/>
       <c r="AA14" s="108"/>
       <c r="AB14" s="108"/>
@@ -20415,20 +20431,20 @@
       <c r="AE14" s="108"/>
     </row>
     <row r="15" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D15" s="190" t="s">
+      <c r="D15" s="189" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="191"/>
+      <c r="E15" s="190"/>
       <c r="F15" s="108"/>
       <c r="G15" s="107"/>
       <c r="H15" s="108"/>
       <c r="I15" s="108"/>
       <c r="J15" s="108"/>
       <c r="K15" s="108"/>
-      <c r="N15" s="192" t="s">
+      <c r="N15" s="191" t="s">
         <v>68</v>
       </c>
-      <c r="O15" s="192"/>
+      <c r="O15" s="191"/>
       <c r="P15" s="108" t="s">
         <v>1591</v>
       </c>
@@ -20437,10 +20453,10 @@
       <c r="S15" s="108"/>
       <c r="T15" s="108"/>
       <c r="U15" s="108"/>
-      <c r="X15" s="192" t="s">
+      <c r="X15" s="191" t="s">
         <v>68</v>
       </c>
-      <c r="Y15" s="192"/>
+      <c r="Y15" s="191"/>
       <c r="Z15" s="108" t="s">
         <v>1590</v>
       </c>
@@ -20451,10 +20467,10 @@
       <c r="AE15" s="108"/>
     </row>
     <row r="16" spans="4:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D16" s="193" t="s">
+      <c r="D16" s="192" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="194"/>
+      <c r="E16" s="193"/>
       <c r="F16" s="108" t="s">
         <v>1588</v>
       </c>
@@ -20465,10 +20481,10 @@
       <c r="I16" s="108"/>
       <c r="J16" s="108"/>
       <c r="K16" s="108"/>
-      <c r="N16" s="184" t="s">
+      <c r="N16" s="196" t="s">
         <v>69</v>
       </c>
-      <c r="O16" s="184"/>
+      <c r="O16" s="196"/>
       <c r="P16" s="108" t="s">
         <v>1587</v>
       </c>
@@ -20477,10 +20493,10 @@
       <c r="S16" s="108"/>
       <c r="T16" s="108"/>
       <c r="U16" s="108"/>
-      <c r="X16" s="184" t="s">
+      <c r="X16" s="196" t="s">
         <v>69</v>
       </c>
-      <c r="Y16" s="184"/>
+      <c r="Y16" s="196"/>
       <c r="Z16" s="108"/>
       <c r="AA16" s="108"/>
       <c r="AB16" s="108"/>
@@ -20489,13 +20505,13 @@
       <c r="AE16" s="108"/>
     </row>
     <row r="17" spans="4:33" ht="15.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="180" t="s">
+      <c r="D17" s="181" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="181"/>
-      <c r="F17" s="181"/>
-      <c r="G17" s="181"/>
-      <c r="H17" s="181"/>
+      <c r="E17" s="182"/>
+      <c r="F17" s="182"/>
+      <c r="G17" s="182"/>
+      <c r="H17" s="182"/>
       <c r="I17" s="105"/>
       <c r="J17" s="106"/>
       <c r="K17" s="106"/>
@@ -20509,13 +20525,13 @@
       <c r="S17" s="185"/>
       <c r="T17" s="185"/>
       <c r="U17" s="185"/>
-      <c r="X17" s="180" t="s">
+      <c r="X17" s="181" t="s">
         <v>70</v>
       </c>
-      <c r="Y17" s="181"/>
-      <c r="Z17" s="181"/>
-      <c r="AA17" s="181"/>
-      <c r="AB17" s="182"/>
+      <c r="Y17" s="182"/>
+      <c r="Z17" s="182"/>
+      <c r="AA17" s="182"/>
+      <c r="AB17" s="183"/>
       <c r="AC17" s="106"/>
       <c r="AD17" s="106"/>
       <c r="AE17" s="106"/>
@@ -20559,10 +20575,10 @@
       <c r="R18" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="S18" s="183" t="s">
+      <c r="S18" s="195" t="s">
         <v>74</v>
       </c>
-      <c r="T18" s="183"/>
+      <c r="T18" s="195"/>
       <c r="U18" s="108" t="s">
         <v>75</v>
       </c>
@@ -20581,10 +20597,10 @@
       <c r="AB18" s="108" t="s">
         <v>73</v>
       </c>
-      <c r="AC18" s="183" t="s">
+      <c r="AC18" s="195" t="s">
         <v>74</v>
       </c>
-      <c r="AD18" s="183"/>
+      <c r="AD18" s="195"/>
       <c r="AE18" s="108" t="s">
         <v>75</v>
       </c>
@@ -20605,8 +20621,8 @@
       <c r="P19" s="21"/>
       <c r="Q19" s="108"/>
       <c r="R19" s="108"/>
-      <c r="S19" s="195"/>
-      <c r="T19" s="183"/>
+      <c r="S19" s="194"/>
+      <c r="T19" s="195"/>
       <c r="U19" s="108"/>
       <c r="X19" s="107">
         <v>45819</v>
@@ -20623,45 +20639,45 @@
       <c r="AB19" s="108" t="s">
         <v>76</v>
       </c>
-      <c r="AC19" s="183"/>
-      <c r="AD19" s="183"/>
+      <c r="AC19" s="195"/>
+      <c r="AD19" s="195"/>
       <c r="AE19" s="108"/>
     </row>
     <row r="20" spans="4:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="4:33" x14ac:dyDescent="0.25">
-      <c r="D21" s="186" t="s">
+      <c r="D21" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="186"/>
-      <c r="F21" s="186"/>
-      <c r="G21" s="186"/>
+      <c r="E21" s="184"/>
+      <c r="F21" s="184"/>
+      <c r="G21" s="184"/>
       <c r="H21" s="22">
         <f ca="1">NOW()</f>
-        <v>45897.784405555554</v>
+        <v>46101.23357488426</v>
       </c>
       <c r="J21" s="22"/>
       <c r="K21" s="22"/>
-      <c r="N21" s="186" t="s">
+      <c r="N21" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="O21" s="186"/>
-      <c r="P21" s="186"/>
-      <c r="Q21" s="186"/>
+      <c r="O21" s="184"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="184"/>
       <c r="R21" s="22">
         <f ca="1">NOW()</f>
-        <v>45897.784405555554</v>
+        <v>46101.23357488426</v>
       </c>
       <c r="T21" s="22"/>
       <c r="U21" s="22"/>
-      <c r="X21" s="186" t="s">
+      <c r="X21" s="184" t="s">
         <v>77</v>
       </c>
-      <c r="Y21" s="186"/>
-      <c r="Z21" s="186"/>
-      <c r="AA21" s="186"/>
+      <c r="Y21" s="184"/>
+      <c r="Z21" s="184"/>
+      <c r="AA21" s="184"/>
       <c r="AB21" s="22">
         <f ca="1">NOW()</f>
-        <v>45897.784405555554</v>
+        <v>46101.23357488426</v>
       </c>
     </row>
     <row r="23" spans="4:33" x14ac:dyDescent="0.25">
@@ -20686,6 +20702,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="X13:AB13"/>
+    <mergeCell ref="AC19:AD19"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="N17:U17"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="X17:AB17"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="X21:AA21"/>
     <mergeCell ref="N21:Q21"/>
@@ -20702,15 +20727,6 @@
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="D13:H13"/>
     <mergeCell ref="S19:T19"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="X13:AB13"/>
-    <mergeCell ref="AC19:AD19"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="N17:U17"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="AC18:AD18"/>
-    <mergeCell ref="X17:AB17"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:H12">
     <cfRule type="expression" dxfId="56" priority="211">
@@ -20807,29 +20823,29 @@
     </row>
     <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
-      <c r="B2" s="240" t="str">
+      <c r="B2" s="208" t="str">
         <f>CONCATENATE("ESCALA DE TRÁFEGO DIÁRIA - ",UPPER(TEXT('ESCALA DO FLUXO'!B2,"Dddd, DD/MM/AAAA")))</f>
-        <v>ESCALA DE TRÁFEGO DIÁRIA - QUINTA-FEIRA, 28/08/2025</v>
-      </c>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="197"/>
-      <c r="G2" s="197"/>
-      <c r="H2" s="198"/>
+        <v>ESCALA DE TRÁFEGO DIÁRIA - SEXTA-FEIRA, 20/03/2026</v>
+      </c>
+      <c r="C2" s="198"/>
+      <c r="D2" s="198"/>
+      <c r="E2" s="198"/>
+      <c r="F2" s="198"/>
+      <c r="G2" s="198"/>
+      <c r="H2" s="199"/>
       <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="8"/>
-      <c r="B3" s="196" t="s">
+      <c r="B3" s="197" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="197"/>
-      <c r="G3" s="197"/>
-      <c r="H3" s="198"/>
+      <c r="C3" s="198"/>
+      <c r="D3" s="198"/>
+      <c r="E3" s="198"/>
+      <c r="F3" s="198"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="199"/>
       <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -20840,10 +20856,10 @@
       <c r="C4" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="196" t="s">
+      <c r="D4" s="197" t="s">
         <v>120</v>
       </c>
-      <c r="E4" s="198"/>
+      <c r="E4" s="199"/>
       <c r="F4" s="109" t="s">
         <v>121</v>
       </c>
@@ -20889,18 +20905,18 @@
       </c>
       <c r="D6" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I2)</f>
-        <v>JOSE ANTONIO INACIO VIEIRA - 5279</v>
+        <v>CLODOALDO PEREIRA DE LIMA - 4067</v>
       </c>
       <c r="E6" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J2)</f>
-        <v>MARCELO RIZO SANTANA - 2048</v>
+        <v>( MOTORISTA DE GOIÂNIA )</v>
       </c>
       <c r="F6" s="114" t="s">
         <v>124</v>
       </c>
       <c r="G6" s="114">
         <f>'ESCALA DO FLUXO'!D2</f>
-        <v>25011</v>
+        <v>25007</v>
       </c>
       <c r="H6" s="114" t="s">
         <v>123</v>
@@ -20918,18 +20934,18 @@
       </c>
       <c r="D7" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I3)</f>
-        <v>VALDIR ALVES MIRANDA - 1364</v>
+        <v>MARCOS ATAIDE SILVA - 1352</v>
       </c>
       <c r="E7" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J3)</f>
-        <v>MANOEL SEVERINO DE SOUZA - 5200</v>
+        <v>FABIO MOREIRA DOS SANTOS - 3073</v>
       </c>
       <c r="F7" s="114" t="s">
         <v>124</v>
       </c>
       <c r="G7" s="114">
         <f>'ESCALA DO FLUXO'!D3</f>
-        <v>24001</v>
+        <v>25011</v>
       </c>
       <c r="H7" s="114" t="s">
         <v>125</v>
@@ -20940,7 +20956,7 @@
       <c r="A8" s="8"/>
       <c r="B8" s="101">
         <f>IF(TEXT('ESCALA DO FLUXO'!A2,"DDDD")="SEXTA",3132,4077)</f>
-        <v>4077</v>
+        <v>3132</v>
       </c>
       <c r="C8" s="99">
         <f>'ESCALA DO FLUXO'!F4</f>
@@ -20948,66 +20964,66 @@
       </c>
       <c r="D8" s="101" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I4)</f>
-        <v>MARCUS AUGUSTO DE CARVALHO - 2398</v>
+        <v>JOSE CARLOS BEZERRA DA SILVA - 3034</v>
       </c>
       <c r="E8" s="101" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J4)</f>
-        <v>LUIS CARLOS VIEIRA DE MELO SOUZA - 5535</v>
+        <v>( MOTORISTA DE GOIÂNIA )</v>
       </c>
       <c r="F8" s="101" t="s">
         <v>124</v>
       </c>
       <c r="G8" s="101">
         <f>'ESCALA DO FLUXO'!D4</f>
-        <v>19018</v>
+        <v>19005</v>
       </c>
       <c r="H8" s="101" t="str">
         <f>IF(TEXT('ESCALA DO FLUXO'!A2,"DDDD")="SEXTA","IMP X PXT","THE X GYN")</f>
-        <v>THE X GYN</v>
+        <v>IMP X PXT</v>
       </c>
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
-      <c r="B9" s="230">
+      <c r="B9" s="204">
         <v>4075</v>
       </c>
-      <c r="C9" s="214">
+      <c r="C9" s="206">
         <v>0.91666666666666663</v>
       </c>
-      <c r="D9" s="212" t="s">
+      <c r="D9" s="209" t="s">
         <v>126</v>
       </c>
-      <c r="E9" s="213"/>
+      <c r="E9" s="210"/>
       <c r="F9" s="111" t="s">
         <v>127</v>
       </c>
-      <c r="G9" s="230">
+      <c r="G9" s="204">
         <f>'ESCALA DO FLUXO'!D13</f>
-        <v>25008</v>
-      </c>
-      <c r="H9" s="210" t="s">
+        <v>25009</v>
+      </c>
+      <c r="H9" s="232" t="s">
         <v>128</v>
       </c>
       <c r="I9" s="8"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="8"/>
-      <c r="B10" s="231"/>
-      <c r="C10" s="215"/>
+      <c r="B10" s="205"/>
+      <c r="C10" s="207"/>
       <c r="D10" s="118" t="str">
         <f>'ESCALA DO FLUXO'!I13</f>
-        <v>EURIPEDES BORGES DOS SANTOS - 5017</v>
-      </c>
-      <c r="E10" s="117" t="str">
+        <v>LUIS ANTONIO FARIAS RIBEIRO - 2789</v>
+      </c>
+      <c r="E10" s="117">
         <f>'ESCALA DO FLUXO'!J13</f>
-        <v>SANDRO CARLOS DE SOUSA - 5181</v>
+        <v>0</v>
       </c>
       <c r="F10" s="119" t="s">
         <v>129</v>
       </c>
-      <c r="G10" s="231"/>
-      <c r="H10" s="211"/>
+      <c r="G10" s="205"/>
+      <c r="H10" s="233"/>
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -21021,18 +21037,18 @@
       </c>
       <c r="D11" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I20)</f>
-        <v>MARCIO DE SOUSA MATOS - 5264</v>
+        <v>CANCELADO</v>
       </c>
       <c r="E11" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J20)</f>
-        <v>NILSON CORTEZ MIRANDA - 5636</v>
+        <v>CANCELADO</v>
       </c>
       <c r="F11" s="114" t="s">
         <v>124</v>
       </c>
-      <c r="G11" s="114">
+      <c r="G11" s="114" t="str">
         <f>'ESCALA DO FLUXO'!D20</f>
-        <v>19006</v>
+        <v>CANCELADO</v>
       </c>
       <c r="H11" s="114" t="s">
         <v>125</v>
@@ -21050,18 +21066,18 @@
       </c>
       <c r="D12" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I21)</f>
-        <v>MERVAL DE SOUSA - 2880</v>
+        <v>KLEBER OLIVEIRA LIMA - 5849</v>
       </c>
       <c r="E12" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J21)</f>
-        <v>JOSE ALVES DE FREITAS NETO - 5027</v>
+        <v/>
       </c>
       <c r="F12" s="114" t="s">
         <v>124</v>
       </c>
       <c r="G12" s="114">
         <f>'ESCALA DO FLUXO'!D21</f>
-        <v>19008</v>
+        <v>19014</v>
       </c>
       <c r="H12" s="114" t="s">
         <v>130</v>
@@ -21079,18 +21095,18 @@
       </c>
       <c r="D13" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I22)</f>
-        <v>RAFAEL JOSE TOME DE LIMA - 5537</v>
+        <v>MARCIO DE SOUSA MATOS - 5264</v>
       </c>
       <c r="E13" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J22)</f>
-        <v>JOAO DA SILVA MORAIS - 2978</v>
+        <v>ANDSON WAGNER NASCIMENTO SOUZA - 2902</v>
       </c>
       <c r="F13" s="114" t="s">
         <v>124</v>
       </c>
       <c r="G13" s="114">
         <f>'ESCALA DO FLUXO'!D22</f>
-        <v>19016</v>
+        <v>19010</v>
       </c>
       <c r="H13" s="114" t="s">
         <v>123</v>
@@ -21099,28 +21115,28 @@
     </row>
     <row r="14" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="8"/>
-      <c r="B14" s="196" t="s">
+      <c r="B14" s="197" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="197"/>
-      <c r="D14" s="197"/>
-      <c r="E14" s="197"/>
-      <c r="F14" s="197"/>
-      <c r="G14" s="197"/>
-      <c r="H14" s="198"/>
+      <c r="C14" s="198"/>
+      <c r="D14" s="198"/>
+      <c r="E14" s="198"/>
+      <c r="F14" s="198"/>
+      <c r="G14" s="198"/>
+      <c r="H14" s="199"/>
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="8"/>
-      <c r="B15" s="196" t="s">
+      <c r="B15" s="197" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="197"/>
-      <c r="D15" s="197"/>
-      <c r="E15" s="197"/>
-      <c r="F15" s="197"/>
-      <c r="G15" s="197"/>
-      <c r="H15" s="198"/>
+      <c r="C15" s="198"/>
+      <c r="D15" s="198"/>
+      <c r="E15" s="198"/>
+      <c r="F15" s="198"/>
+      <c r="G15" s="198"/>
+      <c r="H15" s="199"/>
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -21131,10 +21147,10 @@
       <c r="C16" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="196" t="s">
+      <c r="D16" s="197" t="s">
         <v>120</v>
       </c>
-      <c r="E16" s="198"/>
+      <c r="E16" s="199"/>
       <c r="F16" s="109" t="s">
         <v>121</v>
       </c>
@@ -21148,133 +21164,133 @@
     </row>
     <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="8"/>
-      <c r="B17" s="221">
+      <c r="B17" s="223">
         <v>1125</v>
       </c>
       <c r="C17" s="1">
         <v>0.39513888888888887</v>
       </c>
-      <c r="D17" s="221" t="str">
+      <c r="D17" s="223" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I6)</f>
-        <v>RONNE RODRIGUES DE SOUSA - 5025</v>
-      </c>
-      <c r="E17" s="221"/>
+        <v>EDUARDO SANTOS BEZERRA - 4066</v>
+      </c>
+      <c r="E17" s="223"/>
       <c r="F17" s="114" t="s">
         <v>133</v>
       </c>
-      <c r="G17" s="221">
+      <c r="G17" s="223">
         <f>'ESCALA DO FLUXO'!D6</f>
-        <v>19003</v>
-      </c>
-      <c r="H17" s="218" t="s">
+        <v>19007</v>
+      </c>
+      <c r="H17" s="236" t="s">
         <v>134</v>
       </c>
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
-      <c r="B18" s="221"/>
+      <c r="B18" s="223"/>
       <c r="C18" s="1">
         <v>0.72569444444444442</v>
       </c>
-      <c r="D18" s="221" t="str">
+      <c r="D18" s="223" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J6)</f>
-        <v>MARCOS AUGUSTO SILVA ROCHA - 5268</v>
-      </c>
-      <c r="E18" s="221"/>
+        <v/>
+      </c>
+      <c r="E18" s="223"/>
       <c r="F18" s="114" t="s">
         <v>135</v>
       </c>
-      <c r="G18" s="221"/>
-      <c r="H18" s="218"/>
+      <c r="G18" s="223"/>
+      <c r="H18" s="236"/>
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
-      <c r="B19" s="230">
+      <c r="B19" s="204">
         <v>4074</v>
       </c>
       <c r="C19" s="94">
         <v>0.29166666666666669</v>
       </c>
-      <c r="D19" s="212" t="str">
+      <c r="D19" s="209" t="str">
         <f>'ESCALA DO FLUXO'!I8</f>
-        <v>JWEBISON DE BRITO SOUZA - 2999</v>
-      </c>
-      <c r="E19" s="213"/>
+        <v>MANOEL MESSIAS SILVA DOS SANTOS - 1833</v>
+      </c>
+      <c r="E19" s="210"/>
       <c r="F19" s="111" t="s">
         <v>136</v>
       </c>
-      <c r="G19" s="230">
+      <c r="G19" s="204">
         <f>'ESCALA DO FLUXO'!D8</f>
-        <v>25010</v>
-      </c>
-      <c r="H19" s="210" t="s">
+        <v>25005</v>
+      </c>
+      <c r="H19" s="232" t="s">
         <v>137</v>
       </c>
       <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="8"/>
-      <c r="B20" s="231"/>
+      <c r="B20" s="205"/>
       <c r="C20" s="94">
         <v>0.625</v>
       </c>
-      <c r="D20" s="212" t="str">
+      <c r="D20" s="209">
         <f>'ESCALA DO FLUXO'!J8</f>
-        <v>JOAO FLAVIO DE SOUSA SILVA - 5270</v>
-      </c>
-      <c r="E20" s="213"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="210"/>
       <c r="F20" s="112" t="s">
         <v>138</v>
       </c>
-      <c r="G20" s="231"/>
-      <c r="H20" s="211"/>
+      <c r="G20" s="205"/>
+      <c r="H20" s="233"/>
       <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="8"/>
-      <c r="B21" s="219">
+      <c r="B21" s="215">
         <f>IF(TEXT('ESCALA DO FLUXO'!A2,"DDDD")="SEXTA",9064,4076)</f>
-        <v>4076</v>
+        <v>9064</v>
       </c>
       <c r="C21" s="99">
         <v>0.79861111111111116</v>
       </c>
-      <c r="D21" s="232" t="str">
+      <c r="D21" s="211" t="str">
         <f>'ESCALA DO FLUXO'!I19</f>
-        <v>JERZUALDO DA SILVA GOMES - 4077</v>
-      </c>
-      <c r="E21" s="233"/>
+        <v>FRANCISCO ALVES DA PAZ JUNIOR - 1247</v>
+      </c>
+      <c r="E21" s="212"/>
       <c r="F21" s="113" t="s">
         <v>133</v>
       </c>
-      <c r="G21" s="234">
+      <c r="G21" s="217">
         <f>'ESCALA DO FLUXO'!D19</f>
-        <v>15600</v>
-      </c>
-      <c r="H21" s="219" t="str">
+        <v>19015</v>
+      </c>
+      <c r="H21" s="215" t="str">
         <f>IF(TEXT('ESCALA DO FLUXO'!A2,"DDDD")="SEXTA","IMP X THE","GYN X THE")</f>
-        <v>GYN X THE</v>
+        <v>IMP X THE</v>
       </c>
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="8"/>
-      <c r="B22" s="220"/>
+      <c r="B22" s="216"/>
       <c r="C22" s="100" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="232">
+      <c r="D22" s="211">
         <f>'ESCALA DO FLUXO'!J19</f>
         <v>0</v>
       </c>
-      <c r="E22" s="233"/>
+      <c r="E22" s="212"/>
       <c r="F22" s="113" t="s">
         <v>135</v>
       </c>
-      <c r="G22" s="235"/>
-      <c r="H22" s="220"/>
+      <c r="G22" s="218"/>
+      <c r="H22" s="216"/>
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
@@ -21302,28 +21318,28 @@
     </row>
     <row r="24" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
-      <c r="B24" s="196" t="s">
+      <c r="B24" s="197" t="s">
         <v>141</v>
       </c>
-      <c r="C24" s="197"/>
-      <c r="D24" s="197"/>
-      <c r="E24" s="197"/>
-      <c r="F24" s="197"/>
-      <c r="G24" s="197"/>
-      <c r="H24" s="198"/>
+      <c r="C24" s="198"/>
+      <c r="D24" s="198"/>
+      <c r="E24" s="198"/>
+      <c r="F24" s="198"/>
+      <c r="G24" s="198"/>
+      <c r="H24" s="199"/>
       <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="196" t="s">
+      <c r="B25" s="197" t="s">
         <v>142</v>
       </c>
-      <c r="C25" s="197"/>
-      <c r="D25" s="197"/>
-      <c r="E25" s="197"/>
-      <c r="F25" s="197"/>
-      <c r="G25" s="197"/>
-      <c r="H25" s="198"/>
+      <c r="C25" s="198"/>
+      <c r="D25" s="198"/>
+      <c r="E25" s="198"/>
+      <c r="F25" s="198"/>
+      <c r="G25" s="198"/>
+      <c r="H25" s="199"/>
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -21334,10 +21350,10 @@
       <c r="C26" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="196" t="s">
+      <c r="D26" s="197" t="s">
         <v>143</v>
       </c>
-      <c r="E26" s="198"/>
+      <c r="E26" s="199"/>
       <c r="F26" s="109" t="s">
         <v>121</v>
       </c>
@@ -21359,18 +21375,18 @@
       </c>
       <c r="D27" s="116" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I7)</f>
-        <v>JOAO DE JESUS GOUVEIA - 6016</v>
+        <v>FERNANDO ALVES DE SOUZA - 6350</v>
       </c>
       <c r="E27" s="116" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J7)</f>
-        <v>CLODOALDO PEREIRA DE LIMA - 4067</v>
+        <v>AELSON PEREIRA DO NASCIMENTO - 5682</v>
       </c>
       <c r="F27" s="116" t="s">
         <v>144</v>
       </c>
       <c r="G27" s="114">
         <f>'ESCALA DO FLUXO'!D7</f>
-        <v>19023</v>
+        <v>19021</v>
       </c>
       <c r="H27" s="115" t="s">
         <v>145</v>
@@ -21410,18 +21426,18 @@
       </c>
       <c r="D29" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I15)</f>
-        <v>FRANCISCO BATISTA DE LIMA - 1827</v>
+        <v>BRUNO MATOS DA ROCHA - 6013</v>
       </c>
       <c r="E29" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J15)</f>
-        <v>ADEMILTON DE OLIVEIRA SILVA - 5559</v>
+        <v>ANTONIO FRANCINALDO DE OLIVEIRA MARQUES - 5018</v>
       </c>
       <c r="F29" s="114" t="s">
         <v>144</v>
       </c>
       <c r="G29" s="114">
         <f>'ESCALA DO FLUXO'!D15</f>
-        <v>24005</v>
+        <v>25012</v>
       </c>
       <c r="H29" s="115" t="s">
         <v>145</v>
@@ -21430,28 +21446,28 @@
     </row>
     <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
-      <c r="B30" s="196" t="s">
+      <c r="B30" s="197" t="s">
         <v>131</v>
       </c>
-      <c r="C30" s="197"/>
-      <c r="D30" s="197"/>
-      <c r="E30" s="197"/>
-      <c r="F30" s="197"/>
-      <c r="G30" s="197"/>
-      <c r="H30" s="198"/>
+      <c r="C30" s="198"/>
+      <c r="D30" s="198"/>
+      <c r="E30" s="198"/>
+      <c r="F30" s="198"/>
+      <c r="G30" s="198"/>
+      <c r="H30" s="199"/>
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
-      <c r="B31" s="196" t="s">
+      <c r="B31" s="197" t="s">
         <v>146</v>
       </c>
-      <c r="C31" s="197"/>
-      <c r="D31" s="197"/>
-      <c r="E31" s="197"/>
-      <c r="F31" s="197"/>
-      <c r="G31" s="197"/>
-      <c r="H31" s="198"/>
+      <c r="C31" s="198"/>
+      <c r="D31" s="198"/>
+      <c r="E31" s="198"/>
+      <c r="F31" s="198"/>
+      <c r="G31" s="198"/>
+      <c r="H31" s="199"/>
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -21462,10 +21478,10 @@
       <c r="C32" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D32" s="196" t="s">
+      <c r="D32" s="197" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="198"/>
+      <c r="E32" s="199"/>
       <c r="F32" s="109" t="s">
         <v>121</v>
       </c>
@@ -21487,18 +21503,18 @@
       </c>
       <c r="D33" s="116" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I9)</f>
-        <v>MARCOS ATAIDE SILVA - 1352</v>
+        <v>ANTONIO MARQUES NETO DOS SANTOS - 1738</v>
       </c>
       <c r="E33" s="116" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J9)</f>
-        <v>JARDEL DE SOUSA OLIVEIRA - 5992</v>
+        <v>JERZUALDO DA SILVA GOMES - 4077</v>
       </c>
       <c r="F33" s="116" t="s">
         <v>147</v>
       </c>
       <c r="G33" s="114">
         <f>'ESCALA DO FLUXO'!D9</f>
-        <v>19016</v>
+        <v>19010</v>
       </c>
       <c r="H33" s="115" t="s">
         <v>123</v>
@@ -21539,18 +21555,18 @@
       </c>
       <c r="D35" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I14)</f>
-        <v>REINAN JOSE BORGES SOUSA - 1075</v>
+        <v>JAKTAN DE OLIVEIRA RODRIGUES - 5836</v>
       </c>
       <c r="E35" s="114" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J14)</f>
-        <v>JOSE CARLOS BEZERRA DA SILVA - 3034</v>
+        <v>ARIANO SILVA OLIVEIRA - 6349</v>
       </c>
       <c r="F35" s="114" t="s">
         <v>147</v>
       </c>
       <c r="G35" s="114">
         <f>'ESCALA DO FLUXO'!D14</f>
-        <v>24003</v>
+        <v>24014</v>
       </c>
       <c r="H35" s="115" t="s">
         <v>123</v>
@@ -21559,28 +21575,28 @@
     </row>
     <row r="36" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="8"/>
-      <c r="B36" s="196" t="s">
+      <c r="B36" s="197" t="s">
         <v>131</v>
       </c>
-      <c r="C36" s="197"/>
-      <c r="D36" s="197"/>
-      <c r="E36" s="197"/>
-      <c r="F36" s="197"/>
-      <c r="G36" s="197"/>
-      <c r="H36" s="198"/>
+      <c r="C36" s="198"/>
+      <c r="D36" s="198"/>
+      <c r="E36" s="198"/>
+      <c r="F36" s="198"/>
+      <c r="G36" s="198"/>
+      <c r="H36" s="199"/>
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
-      <c r="B37" s="196" t="s">
+      <c r="B37" s="197" t="s">
         <v>148</v>
       </c>
-      <c r="C37" s="197"/>
-      <c r="D37" s="197"/>
-      <c r="E37" s="197"/>
-      <c r="F37" s="197"/>
-      <c r="G37" s="197"/>
-      <c r="H37" s="198"/>
+      <c r="C37" s="198"/>
+      <c r="D37" s="198"/>
+      <c r="E37" s="198"/>
+      <c r="F37" s="198"/>
+      <c r="G37" s="198"/>
+      <c r="H37" s="199"/>
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -21591,10 +21607,10 @@
       <c r="C38" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D38" s="196" t="s">
+      <c r="D38" s="197" t="s">
         <v>120</v>
       </c>
-      <c r="E38" s="198"/>
+      <c r="E38" s="199"/>
       <c r="F38" s="109" t="s">
         <v>121</v>
       </c>
@@ -21608,153 +21624,153 @@
     </row>
     <row r="39" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="8"/>
-      <c r="B39" s="204">
+      <c r="B39" s="230">
         <v>2260</v>
       </c>
-      <c r="C39" s="216">
+      <c r="C39" s="234">
         <v>0.47013888888888888</v>
       </c>
       <c r="D39" s="224" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I16)</f>
-        <v>KLEBER OLIVEIRA LIMA - 5849</v>
+        <v>FRANCISCO BATISTA DE LIMA - 1827</v>
       </c>
       <c r="E39" s="225"/>
       <c r="F39" s="116" t="s">
         <v>133</v>
       </c>
-      <c r="G39" s="204">
+      <c r="G39" s="230">
         <f>'ESCALA DO FLUXO'!D16</f>
-        <v>19013</v>
-      </c>
-      <c r="H39" s="202" t="s">
+        <v>19024</v>
+      </c>
+      <c r="H39" s="228" t="s">
         <v>149</v>
       </c>
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="8"/>
-      <c r="B40" s="205"/>
-      <c r="C40" s="217"/>
+      <c r="B40" s="231"/>
+      <c r="C40" s="235"/>
       <c r="D40" s="224" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J16)</f>
-        <v>LAUCEANDO DA SILVA ROCHA - 6220</v>
+        <v>EDIVALDO DE ARAUJO - 6217</v>
       </c>
       <c r="E40" s="225"/>
       <c r="F40" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="G40" s="205"/>
-      <c r="H40" s="203"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="229"/>
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
-      <c r="B41" s="230">
+      <c r="B41" s="204">
         <v>4098</v>
       </c>
-      <c r="C41" s="214">
+      <c r="C41" s="206">
         <v>0.8125</v>
       </c>
-      <c r="D41" s="226" t="str">
+      <c r="D41" s="200" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I17)</f>
-        <v>CANCELADO</v>
-      </c>
-      <c r="E41" s="227"/>
+        <v>REGINALDO DE SOUSA OLIVEIRA - 5412</v>
+      </c>
+      <c r="E41" s="201"/>
       <c r="F41" s="119" t="s">
         <v>133</v>
       </c>
-      <c r="G41" s="230" t="str">
+      <c r="G41" s="204">
         <f>'ESCALA DO FLUXO'!D17</f>
-        <v>CANCELADO</v>
-      </c>
-      <c r="H41" s="228" t="s">
+        <v>18016</v>
+      </c>
+      <c r="H41" s="202" t="s">
         <v>151</v>
       </c>
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>
-      <c r="B42" s="231"/>
-      <c r="C42" s="215"/>
-      <c r="D42" s="226" t="str">
+      <c r="B42" s="205"/>
+      <c r="C42" s="207"/>
+      <c r="D42" s="200" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J17)</f>
-        <v>CANCELADO</v>
-      </c>
-      <c r="E42" s="227"/>
+        <v>JOSE ANTONIO OLIVEIRA SILVA NETO - 6378</v>
+      </c>
+      <c r="E42" s="201"/>
       <c r="F42" s="119" t="s">
         <v>150</v>
       </c>
-      <c r="G42" s="231"/>
-      <c r="H42" s="229"/>
+      <c r="G42" s="205"/>
+      <c r="H42" s="203"/>
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>
-      <c r="B43" s="236">
+      <c r="B43" s="219">
         <v>1071</v>
       </c>
       <c r="C43" s="97">
         <v>0.84375</v>
       </c>
-      <c r="D43" s="238" t="str">
+      <c r="D43" s="221" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I18)</f>
-        <v>ANTONIO MARQUES NETO DOS SANTOS - 1738</v>
-      </c>
-      <c r="E43" s="239"/>
+        <v>JARDEL DE SOUSA OLIVEIRA - 5992</v>
+      </c>
+      <c r="E43" s="222"/>
       <c r="F43" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="G43" s="236">
+      <c r="G43" s="219">
         <f>'ESCALA DO FLUXO'!D18</f>
-        <v>24004</v>
-      </c>
-      <c r="H43" s="222" t="s">
+        <v>25008</v>
+      </c>
+      <c r="H43" s="226" t="s">
         <v>149</v>
       </c>
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="8"/>
-      <c r="B44" s="237"/>
+      <c r="B44" s="220"/>
       <c r="C44" s="97">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="D44" s="238" t="str">
+      <c r="D44" s="221" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I19)</f>
-        <v>JERZUALDO DA SILVA GOMES - 4077</v>
-      </c>
-      <c r="E44" s="239"/>
+        <v>FRANCISCO ALVES DA PAZ JUNIOR - 1247</v>
+      </c>
+      <c r="E44" s="222"/>
       <c r="F44" s="98" t="s">
         <v>150</v>
       </c>
-      <c r="G44" s="237"/>
-      <c r="H44" s="223"/>
+      <c r="G44" s="220"/>
+      <c r="H44" s="227"/>
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="8"/>
-      <c r="B45" s="196" t="s">
+      <c r="B45" s="197" t="s">
         <v>131</v>
       </c>
-      <c r="C45" s="197"/>
-      <c r="D45" s="197"/>
-      <c r="E45" s="197"/>
-      <c r="F45" s="197"/>
-      <c r="G45" s="197"/>
-      <c r="H45" s="198"/>
+      <c r="C45" s="198"/>
+      <c r="D45" s="198"/>
+      <c r="E45" s="198"/>
+      <c r="F45" s="198"/>
+      <c r="G45" s="198"/>
+      <c r="H45" s="199"/>
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="8"/>
-      <c r="B46" s="196" t="s">
+      <c r="B46" s="197" t="s">
         <v>152</v>
       </c>
-      <c r="C46" s="197"/>
-      <c r="D46" s="197"/>
-      <c r="E46" s="197"/>
-      <c r="F46" s="197"/>
-      <c r="G46" s="197"/>
-      <c r="H46" s="198"/>
+      <c r="C46" s="198"/>
+      <c r="D46" s="198"/>
+      <c r="E46" s="198"/>
+      <c r="F46" s="198"/>
+      <c r="G46" s="198"/>
+      <c r="H46" s="199"/>
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -21765,10 +21781,10 @@
       <c r="C47" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D47" s="196" t="s">
+      <c r="D47" s="197" t="s">
         <v>120</v>
       </c>
-      <c r="E47" s="198"/>
+      <c r="E47" s="199"/>
       <c r="F47" s="109" t="s">
         <v>121</v>
       </c>
@@ -21782,155 +21798,155 @@
     </row>
     <row r="48" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
-      <c r="B48" s="228">
+      <c r="B48" s="202">
         <v>2261</v>
       </c>
       <c r="C48" s="95">
         <v>0.29166666666666669</v>
       </c>
-      <c r="D48" s="226" t="str">
+      <c r="D48" s="200" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I10)</f>
-        <v>EDIVALDO DE ARAUJO - 6217</v>
-      </c>
-      <c r="E48" s="227"/>
+        <v>CARLOS ADRIANO DE SOUZA DO NASCIMENTO - 6222</v>
+      </c>
+      <c r="E48" s="201"/>
       <c r="F48" s="119" t="s">
         <v>153</v>
       </c>
-      <c r="G48" s="230">
+      <c r="G48" s="204">
         <f>'ESCALA DO FLUXO'!D10</f>
-        <v>19006</v>
-      </c>
-      <c r="H48" s="228" t="s">
+        <v>20015</v>
+      </c>
+      <c r="H48" s="202" t="s">
         <v>125</v>
       </c>
       <c r="I48" s="8"/>
     </row>
     <row r="49" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
-      <c r="B49" s="229"/>
+      <c r="B49" s="203"/>
       <c r="C49" s="95">
         <v>0.52083333333333337</v>
       </c>
-      <c r="D49" s="226" t="str">
+      <c r="D49" s="200" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J10)</f>
-        <v>ANTONIO RAMIRO WEBER - 5452</v>
-      </c>
-      <c r="E49" s="227"/>
+        <v>LEANDRO DE OLIVEIRA MELO - 2151</v>
+      </c>
+      <c r="E49" s="201"/>
       <c r="F49" s="119" t="s">
         <v>154</v>
       </c>
-      <c r="G49" s="231"/>
-      <c r="H49" s="229"/>
+      <c r="G49" s="205"/>
+      <c r="H49" s="203"/>
       <c r="I49" s="8"/>
     </row>
     <row r="50" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
-      <c r="B50" s="202">
+      <c r="B50" s="228">
         <v>4099</v>
       </c>
-      <c r="C50" s="200">
+      <c r="C50" s="238">
         <v>0.79513888888888884</v>
       </c>
-      <c r="D50" s="208" t="str">
+      <c r="D50" s="213" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I12)</f>
         <v>CANCELADO</v>
       </c>
-      <c r="E50" s="209"/>
+      <c r="E50" s="214"/>
       <c r="F50" s="134" t="s">
         <v>133</v>
       </c>
-      <c r="G50" s="204" t="str">
+      <c r="G50" s="230" t="str">
         <f>'ESCALA DO FLUXO'!D12</f>
         <v>CANCELADO</v>
       </c>
-      <c r="H50" s="202" t="s">
+      <c r="H50" s="228" t="s">
         <v>155</v>
       </c>
       <c r="I50" s="8"/>
     </row>
     <row r="51" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
-      <c r="B51" s="203"/>
-      <c r="C51" s="201"/>
-      <c r="D51" s="208" t="str">
+      <c r="B51" s="229"/>
+      <c r="C51" s="239"/>
+      <c r="D51" s="213" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J12)</f>
         <v>CANCELADO</v>
       </c>
-      <c r="E51" s="209"/>
+      <c r="E51" s="214"/>
       <c r="F51" s="134" t="s">
         <v>154</v>
       </c>
-      <c r="G51" s="205"/>
-      <c r="H51" s="203"/>
+      <c r="G51" s="231"/>
+      <c r="H51" s="229"/>
       <c r="I51" s="8"/>
     </row>
     <row r="52" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>
-      <c r="B52" s="207">
+      <c r="B52" s="241">
         <v>1072</v>
       </c>
       <c r="C52" s="95">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D52" s="206" t="str">
+      <c r="D52" s="240" t="str">
         <f>TRIM('ESCALA DO FLUXO'!I11)</f>
         <v>KAYLSON KLEYTON DA SILVA COSTA - 6224</v>
       </c>
-      <c r="E52" s="206"/>
+      <c r="E52" s="240"/>
       <c r="F52" s="111" t="s">
         <v>153</v>
       </c>
-      <c r="G52" s="206">
+      <c r="G52" s="240">
         <f>'ESCALA DO FLUXO'!D11</f>
-        <v>25006</v>
-      </c>
-      <c r="H52" s="207" t="s">
+        <v>25005</v>
+      </c>
+      <c r="H52" s="241" t="s">
         <v>125</v>
       </c>
       <c r="I52" s="8"/>
     </row>
     <row r="53" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="8"/>
-      <c r="B53" s="207"/>
+      <c r="B53" s="241"/>
       <c r="C53" s="96" t="s">
         <v>156</v>
       </c>
-      <c r="D53" s="206" t="str">
+      <c r="D53" s="240" t="str">
         <f>TRIM('ESCALA DO FLUXO'!J11)</f>
-        <v>ELIEZIO JOSE DOS SANTOS - 2645</v>
-      </c>
-      <c r="E53" s="206"/>
+        <v>JARDEL DE SOUSA OLIVEIRA - 5992</v>
+      </c>
+      <c r="E53" s="240"/>
       <c r="F53" s="111" t="s">
         <v>154</v>
       </c>
-      <c r="G53" s="206"/>
-      <c r="H53" s="207"/>
+      <c r="G53" s="240"/>
+      <c r="H53" s="241"/>
       <c r="I53" s="8"/>
     </row>
     <row r="54" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
-      <c r="B54" s="196" t="s">
+      <c r="B54" s="197" t="s">
         <v>131</v>
       </c>
-      <c r="C54" s="197"/>
-      <c r="D54" s="197"/>
-      <c r="E54" s="197"/>
-      <c r="F54" s="197"/>
-      <c r="G54" s="197"/>
-      <c r="H54" s="198"/>
+      <c r="C54" s="198"/>
+      <c r="D54" s="198"/>
+      <c r="E54" s="198"/>
+      <c r="F54" s="198"/>
+      <c r="G54" s="198"/>
+      <c r="H54" s="199"/>
       <c r="I54" s="8"/>
     </row>
     <row r="55" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
-      <c r="B55" s="196" t="s">
+      <c r="B55" s="197" t="s">
         <v>157</v>
       </c>
-      <c r="C55" s="197"/>
-      <c r="D55" s="197"/>
-      <c r="E55" s="197"/>
-      <c r="F55" s="197"/>
-      <c r="G55" s="197"/>
-      <c r="H55" s="198"/>
+      <c r="C55" s="198"/>
+      <c r="D55" s="198"/>
+      <c r="E55" s="198"/>
+      <c r="F55" s="198"/>
+      <c r="G55" s="198"/>
+      <c r="H55" s="199"/>
       <c r="I55" s="8"/>
     </row>
     <row r="56" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
@@ -21941,10 +21957,10 @@
       <c r="C56" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D56" s="199" t="s">
+      <c r="D56" s="237" t="s">
         <v>120</v>
       </c>
-      <c r="E56" s="199"/>
+      <c r="E56" s="237"/>
       <c r="F56" s="109" t="s">
         <v>121</v>
       </c>
@@ -21987,28 +22003,28 @@
     </row>
     <row r="58" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8"/>
-      <c r="B58" s="196" t="s">
+      <c r="B58" s="197" t="s">
         <v>131</v>
       </c>
-      <c r="C58" s="197"/>
-      <c r="D58" s="197"/>
-      <c r="E58" s="197"/>
-      <c r="F58" s="197"/>
-      <c r="G58" s="197"/>
-      <c r="H58" s="198"/>
+      <c r="C58" s="198"/>
+      <c r="D58" s="198"/>
+      <c r="E58" s="198"/>
+      <c r="F58" s="198"/>
+      <c r="G58" s="198"/>
+      <c r="H58" s="199"/>
       <c r="I58" s="8"/>
     </row>
     <row r="59" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8"/>
-      <c r="B59" s="196" t="s">
+      <c r="B59" s="197" t="s">
         <v>1567</v>
       </c>
-      <c r="C59" s="197"/>
-      <c r="D59" s="197"/>
-      <c r="E59" s="197"/>
-      <c r="F59" s="197"/>
-      <c r="G59" s="197"/>
-      <c r="H59" s="198"/>
+      <c r="C59" s="198"/>
+      <c r="D59" s="198"/>
+      <c r="E59" s="198"/>
+      <c r="F59" s="198"/>
+      <c r="G59" s="198"/>
+      <c r="H59" s="199"/>
       <c r="I59" s="8"/>
     </row>
     <row r="60" spans="1:9" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
@@ -22019,10 +22035,10 @@
       <c r="C60" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D60" s="199" t="s">
+      <c r="D60" s="237" t="s">
         <v>120</v>
       </c>
-      <c r="E60" s="199"/>
+      <c r="E60" s="237"/>
       <c r="F60" s="109" t="s">
         <v>121</v>
       </c>
@@ -22119,14 +22135,59 @@
     <protectedRange sqref="F19:F43 E44:E47 D54:E57 G11:H43 B11:C57 E19:E38 B2:H9 D10:F10 E11:F16 D11:D53 F44:H57 B58:H61 A62:I64" name="ESCALA MESCLADA"/>
   </protectedRanges>
   <mergeCells count="77">
-    <mergeCell ref="B46:H46"/>
-    <mergeCell ref="B45:H45"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B59:H59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="B54:H54"/>
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="G41:G42"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D32:E32"/>
     <mergeCell ref="B41:B42"/>
     <mergeCell ref="C41:C42"/>
     <mergeCell ref="B2:H2"/>
@@ -22143,59 +22204,14 @@
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="G43:G44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="G41:G42"/>
-    <mergeCell ref="G39:G40"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="B58:H58"/>
-    <mergeCell ref="B59:H59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="G50:G51"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="B54:H54"/>
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="G52:G53"/>
-    <mergeCell ref="H52:H53"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="H48:H49"/>
   </mergeCells>
   <conditionalFormatting sqref="A64:E64">
     <cfRule type="containsText" dxfId="42" priority="1" operator="containsText" text="CANCELADO">
@@ -22320,130 +22336,130 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="250" t="s">
-        <v>1595</v>
-      </c>
-      <c r="B2" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C2" s="136" t="s">
+      <c r="A2" s="248" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B2" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C2" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="136">
+      <c r="D2" s="160">
+        <v>25007</v>
+      </c>
+      <c r="E2" s="161">
+        <v>0.25486111111111109</v>
+      </c>
+      <c r="F2" s="161">
+        <v>0.3</v>
+      </c>
+      <c r="G2" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="160" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="160" t="s">
+        <v>932</v>
+      </c>
+      <c r="J2" s="160" t="s">
+        <v>1597</v>
+      </c>
+      <c r="K2" s="160" t="s">
+        <v>89</v>
+      </c>
+      <c r="L2" s="162"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="249"/>
+      <c r="B3" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C3" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="160">
         <v>25011</v>
       </c>
-      <c r="E2" s="137">
-        <v>0.25486111111111109</v>
-      </c>
-      <c r="F2" s="137">
-        <v>0.3</v>
-      </c>
-      <c r="G2" s="136" t="s">
+      <c r="E3" s="161">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="F3" s="161">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G3" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="136" t="s">
+      <c r="H3" s="160" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="136" t="s">
-        <v>1162</v>
-      </c>
-      <c r="J2" s="136" t="s">
-        <v>511</v>
-      </c>
-      <c r="K2" s="136" t="s">
-        <v>89</v>
-      </c>
-      <c r="L2" s="164"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="251"/>
-      <c r="B3" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C3" s="136" t="s">
+      <c r="I3" s="160" t="s">
+        <v>104</v>
+      </c>
+      <c r="J3" s="160" t="s">
+        <v>844</v>
+      </c>
+      <c r="K3" s="160" t="s">
+        <v>90</v>
+      </c>
+      <c r="L3" s="162"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="249"/>
+      <c r="B4" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C4" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="136">
-        <v>24001</v>
-      </c>
-      <c r="E3" s="137">
-        <v>0.32291666666666669</v>
-      </c>
-      <c r="F3" s="137">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="G3" s="136" t="s">
+      <c r="D4" s="160">
+        <v>19005</v>
+      </c>
+      <c r="E4" s="161">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="F4" s="161">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="G4" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="H3" s="136" t="s">
+      <c r="H4" s="160" t="s">
         <v>57</v>
       </c>
-      <c r="I3" s="136" t="s">
-        <v>317</v>
-      </c>
-      <c r="J3" s="136" t="s">
-        <v>1068</v>
-      </c>
-      <c r="K3" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="L3" s="164"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="251"/>
-      <c r="B4" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C4" s="136" t="s">
+      <c r="I4" s="160" t="s">
+        <v>826</v>
+      </c>
+      <c r="J4" s="160" t="s">
+        <v>1597</v>
+      </c>
+      <c r="K4" s="160" t="s">
+        <v>92</v>
+      </c>
+      <c r="L4" s="162"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="249"/>
+      <c r="B5" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C5" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="136">
-        <v>19018</v>
-      </c>
-      <c r="E4" s="137">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="F4" s="137">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="G4" s="136" t="s">
+      <c r="D5" s="156" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="161">
+        <v>0.375</v>
+      </c>
+      <c r="F5" s="161">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G5" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="H4" s="136" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="136" t="s">
-        <v>561</v>
-      </c>
-      <c r="J4" s="136" t="s">
-        <v>1418</v>
-      </c>
-      <c r="K4" s="136" t="s">
-        <v>92</v>
-      </c>
-      <c r="L4" s="164"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="251"/>
-      <c r="B5" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C5" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="162" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" s="137">
-        <v>0.375</v>
-      </c>
-      <c r="F5" s="137">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="G5" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="136" t="s">
+      <c r="H5" s="160" t="s">
         <v>63</v>
       </c>
       <c r="I5" s="156" t="s">
@@ -22452,234 +22468,232 @@
       <c r="J5" s="156" t="s">
         <v>93</v>
       </c>
-      <c r="K5" s="136"/>
-      <c r="L5" s="164"/>
+      <c r="K5" s="160" t="s">
+        <v>1598</v>
+      </c>
+      <c r="L5" s="162"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="251"/>
-      <c r="B6" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C6" s="136" t="s">
+      <c r="A6" s="249"/>
+      <c r="B6" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C6" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="136">
-        <v>19003</v>
-      </c>
-      <c r="E6" s="137">
+      <c r="D6" s="160">
+        <v>19007</v>
+      </c>
+      <c r="E6" s="161">
         <v>0.3888888888888889</v>
       </c>
-      <c r="F6" s="137">
+      <c r="F6" s="161">
         <v>0.37708333333333333</v>
       </c>
-      <c r="G6" s="136" t="s">
+      <c r="G6" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="136" t="s">
+      <c r="H6" s="160" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="163" t="s">
-        <v>974</v>
-      </c>
-      <c r="J6" s="163" t="s">
-        <v>1143</v>
-      </c>
-      <c r="K6" s="136" t="s">
+      <c r="I6" s="160" t="s">
+        <v>109</v>
+      </c>
+      <c r="J6" s="160"/>
+      <c r="K6" s="160" t="s">
         <v>96</v>
       </c>
-      <c r="L6" s="164"/>
+      <c r="L6" s="162"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="251"/>
-      <c r="B7" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C7" s="136" t="s">
+      <c r="A7" s="249"/>
+      <c r="B7" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C7" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D7" s="136">
-        <v>19023</v>
-      </c>
-      <c r="E7" s="137">
+      <c r="D7" s="160">
+        <v>19021</v>
+      </c>
+      <c r="E7" s="161">
         <v>0.38958333333333334</v>
       </c>
-      <c r="F7" s="137">
+      <c r="F7" s="161">
         <v>0.38541666666666669</v>
       </c>
-      <c r="G7" s="136" t="s">
+      <c r="G7" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="136" t="s">
+      <c r="H7" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="136" t="s">
-        <v>1596</v>
-      </c>
-      <c r="J7" s="136" t="s">
-        <v>932</v>
-      </c>
-      <c r="K7" s="136" t="s">
+      <c r="I7" s="160" t="s">
+        <v>1599</v>
+      </c>
+      <c r="J7" s="160" t="s">
+        <v>1550</v>
+      </c>
+      <c r="K7" s="160" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="164"/>
+      <c r="L7" s="162"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="251"/>
-      <c r="B8" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C8" s="136" t="s">
+      <c r="A8" s="249"/>
+      <c r="B8" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C8" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="136">
-        <v>25010</v>
-      </c>
-      <c r="E8" s="137">
+      <c r="D8" s="160">
+        <v>25005</v>
+      </c>
+      <c r="E8" s="161">
         <v>0.375</v>
       </c>
-      <c r="F8" s="137">
+      <c r="F8" s="161">
         <v>0.39930555555555558</v>
       </c>
-      <c r="G8" s="136" t="s">
+      <c r="G8" s="160" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="136" t="s">
+      <c r="H8" s="160" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="163" t="s">
-        <v>100</v>
-      </c>
-      <c r="J8" s="163" t="s">
-        <v>1147</v>
-      </c>
-      <c r="K8" s="136" t="s">
+      <c r="I8" s="160" t="s">
+        <v>102</v>
+      </c>
+      <c r="J8" s="160"/>
+      <c r="K8" s="160" t="s">
         <v>101</v>
       </c>
-      <c r="L8" s="164"/>
+      <c r="L8" s="162"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="251"/>
-      <c r="B9" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C9" s="136" t="s">
+      <c r="A9" s="249"/>
+      <c r="B9" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C9" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D9" s="136">
-        <v>19016</v>
-      </c>
-      <c r="E9" s="137">
+      <c r="D9" s="160">
+        <v>19010</v>
+      </c>
+      <c r="E9" s="161">
         <v>0.375</v>
       </c>
-      <c r="F9" s="137">
+      <c r="F9" s="161">
         <v>0.41666666666666669</v>
       </c>
-      <c r="G9" s="136" t="s">
+      <c r="G9" s="160" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="136" t="s">
+      <c r="H9" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="136" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="136" t="s">
+      <c r="I9" s="160" t="s">
+        <v>103</v>
+      </c>
+      <c r="J9" s="160" t="s">
+        <v>938</v>
+      </c>
+      <c r="K9" s="160" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="162"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="249"/>
+      <c r="B10" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C10" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="160">
+        <v>20015</v>
+      </c>
+      <c r="E10" s="161">
+        <v>0.25</v>
+      </c>
+      <c r="F10" s="161">
+        <v>0.29166666666666669</v>
+      </c>
+      <c r="G10" s="160" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="160" t="s">
+        <v>1600</v>
+      </c>
+      <c r="J10" s="160" t="s">
+        <v>111</v>
+      </c>
+      <c r="K10" s="160" t="s">
+        <v>90</v>
+      </c>
+      <c r="L10" s="162"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="249"/>
+      <c r="B11" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C11" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="160">
+        <v>25005</v>
+      </c>
+      <c r="E11" s="161">
+        <v>0.75</v>
+      </c>
+      <c r="F11" s="161">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="G11" s="160" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="160" t="s">
+        <v>1593</v>
+      </c>
+      <c r="J11" s="160" t="s">
         <v>1594</v>
       </c>
-      <c r="K9" s="136" t="s">
-        <v>89</v>
-      </c>
-      <c r="L9" s="164"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="251"/>
-      <c r="B10" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C10" s="136" t="s">
+      <c r="K11" s="160" t="s">
+        <v>90</v>
+      </c>
+      <c r="L11" s="162"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="249"/>
+      <c r="B12" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C12" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="136">
-        <v>19006</v>
-      </c>
-      <c r="E10" s="137">
-        <v>0.25</v>
-      </c>
-      <c r="F10" s="137">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="G10" s="136" t="s">
+      <c r="D12" s="156" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="161">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F12" s="161">
+        <v>0.79513888888888884</v>
+      </c>
+      <c r="G12" s="160" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" s="136" t="s">
-        <v>1597</v>
-      </c>
-      <c r="J10" s="136" t="s">
-        <v>97</v>
-      </c>
-      <c r="K10" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="L10" s="164"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="251"/>
-      <c r="B11" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C11" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" s="136">
-        <v>25006</v>
-      </c>
-      <c r="E11" s="137">
-        <v>0.75</v>
-      </c>
-      <c r="F11" s="137">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="G11" s="136" t="s">
-        <v>58</v>
-      </c>
-      <c r="H11" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" s="136" t="s">
-        <v>1593</v>
-      </c>
-      <c r="J11" s="136" t="s">
-        <v>661</v>
-      </c>
-      <c r="K11" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="L11" s="164"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="251"/>
-      <c r="B12" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C12" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="162" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="137">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F12" s="137">
-        <v>0.79513888888888884</v>
-      </c>
-      <c r="G12" s="136" t="s">
-        <v>58</v>
-      </c>
-      <c r="H12" s="136" t="s">
+      <c r="H12" s="160" t="s">
         <v>59</v>
       </c>
       <c r="I12" s="156" t="s">
@@ -22688,348 +22702,344 @@
       <c r="J12" s="156" t="s">
         <v>93</v>
       </c>
-      <c r="K12" s="136" t="s">
+      <c r="K12" s="160" t="s">
         <v>105</v>
       </c>
-      <c r="L12" s="164"/>
+      <c r="L12" s="162"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="251"/>
-      <c r="B13" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C13" s="136" t="s">
+      <c r="A13" s="249"/>
+      <c r="B13" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C13" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="136">
+      <c r="D13" s="160">
+        <v>25009</v>
+      </c>
+      <c r="E13" s="161">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="F13" s="161">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G13" s="160" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="160" t="s">
+        <v>57</v>
+      </c>
+      <c r="I13" s="160" t="s">
+        <v>734</v>
+      </c>
+      <c r="J13" s="160"/>
+      <c r="K13" s="160" t="s">
+        <v>101</v>
+      </c>
+      <c r="L13" s="162"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="249"/>
+      <c r="B14" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C14" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="160">
+        <v>24014</v>
+      </c>
+      <c r="E14" s="161">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F14" s="161">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="G14" s="160" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="160" t="s">
+        <v>1601</v>
+      </c>
+      <c r="J14" s="160" t="s">
+        <v>1602</v>
+      </c>
+      <c r="K14" s="160" t="s">
+        <v>89</v>
+      </c>
+      <c r="L14" s="162"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="249"/>
+      <c r="B15" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C15" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="160">
+        <v>25012</v>
+      </c>
+      <c r="E15" s="161">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="F15" s="161">
+        <v>0.82777777777777772</v>
+      </c>
+      <c r="G15" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="160" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="160" t="s">
+        <v>1571</v>
+      </c>
+      <c r="J15" s="160" t="s">
+        <v>964</v>
+      </c>
+      <c r="K15" s="160" t="s">
+        <v>89</v>
+      </c>
+      <c r="L15" s="162"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="249"/>
+      <c r="B16" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C16" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="160">
+        <v>19024</v>
+      </c>
+      <c r="E16" s="161">
+        <v>0.40763888888888888</v>
+      </c>
+      <c r="F16" s="161">
+        <v>0.47013888888888888</v>
+      </c>
+      <c r="G16" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="160" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="160" t="s">
+        <v>431</v>
+      </c>
+      <c r="J16" s="160" t="s">
+        <v>1595</v>
+      </c>
+      <c r="K16" s="160" t="s">
+        <v>90</v>
+      </c>
+      <c r="L16" s="162"/>
+    </row>
+    <row r="17" spans="1:12" s="62" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="249"/>
+      <c r="B17" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C17" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="160">
+        <v>18016</v>
+      </c>
+      <c r="E17" s="161">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F17" s="161">
+        <v>0.8125</v>
+      </c>
+      <c r="G17" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="160" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" s="160" t="s">
+        <v>1313</v>
+      </c>
+      <c r="J17" s="160" t="s">
+        <v>1603</v>
+      </c>
+      <c r="K17" s="160" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" s="162"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="249"/>
+      <c r="B18" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C18" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="160">
         <v>25008</v>
       </c>
-      <c r="E13" s="137">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="F13" s="137">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="G13" s="136" t="s">
-        <v>99</v>
-      </c>
-      <c r="H13" s="136" t="s">
+      <c r="E18" s="161">
+        <v>0.8125</v>
+      </c>
+      <c r="F18" s="161">
+        <v>0.84375</v>
+      </c>
+      <c r="G18" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="160" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="160" t="s">
+        <v>1594</v>
+      </c>
+      <c r="J18" s="160" t="s">
+        <v>1593</v>
+      </c>
+      <c r="K18" s="160" t="s">
+        <v>90</v>
+      </c>
+      <c r="L18" s="162"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="249"/>
+      <c r="B19" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C19" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="160">
+        <v>19015</v>
+      </c>
+      <c r="E19" s="161">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="F19" s="161">
+        <v>0.79861111111111116</v>
+      </c>
+      <c r="G19" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="160" t="s">
+        <v>62</v>
+      </c>
+      <c r="I19" s="160" t="s">
+        <v>294</v>
+      </c>
+      <c r="J19" s="160"/>
+      <c r="K19" s="160" t="s">
+        <v>92</v>
+      </c>
+      <c r="L19" s="162"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="249"/>
+      <c r="B20" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C20" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="156" t="s">
+        <v>93</v>
+      </c>
+      <c r="E20" s="161">
+        <v>0.8125</v>
+      </c>
+      <c r="F20" s="161">
+        <v>0.84166666666666667</v>
+      </c>
+      <c r="G20" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="160" t="s">
         <v>57</v>
       </c>
-      <c r="I13" s="136" t="s">
-        <v>962</v>
-      </c>
-      <c r="J13" s="136" t="s">
-        <v>1038</v>
-      </c>
-      <c r="K13" s="136" t="s">
-        <v>101</v>
-      </c>
-      <c r="L13" s="164"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="251"/>
-      <c r="B14" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C14" s="136" t="s">
+      <c r="I20" s="156" t="s">
+        <v>93</v>
+      </c>
+      <c r="J20" s="156" t="s">
+        <v>93</v>
+      </c>
+      <c r="K20" s="160" t="s">
+        <v>90</v>
+      </c>
+      <c r="L20" s="162"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="249"/>
+      <c r="B21" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C21" s="160" t="s">
         <v>86</v>
       </c>
-      <c r="D14" s="136">
-        <v>24003</v>
-      </c>
-      <c r="E14" s="137">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="F14" s="137">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="G14" s="136" t="s">
-        <v>56</v>
-      </c>
-      <c r="H14" s="136" t="s">
+      <c r="D21" s="160">
+        <v>19014</v>
+      </c>
+      <c r="E21" s="161">
+        <v>0.8125</v>
+      </c>
+      <c r="F21" s="161">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="G21" s="160" t="s">
         <v>59</v>
       </c>
-      <c r="I14" s="136" t="s">
-        <v>262</v>
-      </c>
-      <c r="J14" s="136" t="s">
-        <v>826</v>
-      </c>
-      <c r="K14" s="136" t="s">
+      <c r="H21" s="160" t="s">
+        <v>57</v>
+      </c>
+      <c r="I21" s="160" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J21" s="160"/>
+      <c r="K21" s="160" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="162"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="249"/>
+      <c r="B22" s="159">
+        <v>46101</v>
+      </c>
+      <c r="C22" s="160" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="160">
+        <v>19010</v>
+      </c>
+      <c r="E22" s="161">
+        <v>0.84722222222222221</v>
+      </c>
+      <c r="F22" s="161">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="G22" s="160" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="160" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="160" t="s">
+        <v>112</v>
+      </c>
+      <c r="J22" s="160" t="s">
+        <v>750</v>
+      </c>
+      <c r="K22" s="160" t="s">
         <v>89</v>
       </c>
-      <c r="L14" s="164"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="251"/>
-      <c r="B15" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C15" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="136">
-        <v>24005</v>
-      </c>
-      <c r="E15" s="137">
-        <v>0.76041666666666663</v>
-      </c>
-      <c r="F15" s="137">
-        <v>0.82777777777777772</v>
-      </c>
-      <c r="G15" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="136" t="s">
-        <v>56</v>
-      </c>
-      <c r="I15" s="136" t="s">
-        <v>431</v>
-      </c>
-      <c r="J15" s="136" t="s">
-        <v>1451</v>
-      </c>
-      <c r="K15" s="136" t="s">
-        <v>89</v>
-      </c>
-      <c r="L15" s="164"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="251"/>
-      <c r="B16" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C16" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="136">
-        <v>19013</v>
-      </c>
-      <c r="E16" s="137">
-        <v>0.40763888888888888</v>
-      </c>
-      <c r="F16" s="137">
-        <v>0.47013888888888888</v>
-      </c>
-      <c r="G16" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="H16" s="136" t="s">
-        <v>58</v>
-      </c>
-      <c r="I16" s="136" t="s">
-        <v>1592</v>
-      </c>
-      <c r="J16" s="136" t="s">
-        <v>1582</v>
-      </c>
-      <c r="K16" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="L16" s="164"/>
-    </row>
-    <row r="17" spans="1:12" s="62" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="251"/>
-      <c r="B17" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C17" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="162" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="137">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F17" s="137">
-        <v>0.8125</v>
-      </c>
-      <c r="G17" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="H17" s="136" t="s">
-        <v>58</v>
-      </c>
-      <c r="I17" s="156" t="s">
-        <v>93</v>
-      </c>
-      <c r="J17" s="156" t="s">
-        <v>93</v>
-      </c>
-      <c r="K17" s="136" t="s">
-        <v>105</v>
-      </c>
-      <c r="L17" s="164"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="251"/>
-      <c r="B18" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C18" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="136">
-        <v>24004</v>
-      </c>
-      <c r="E18" s="137">
-        <v>0.8125</v>
-      </c>
-      <c r="F18" s="137">
-        <v>0.84375</v>
-      </c>
-      <c r="G18" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" s="136" t="s">
-        <v>58</v>
-      </c>
-      <c r="I18" s="136" t="s">
-        <v>103</v>
-      </c>
-      <c r="J18" s="136" t="s">
-        <v>1597</v>
-      </c>
-      <c r="K18" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="L18" s="164"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="251"/>
-      <c r="B19" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C19" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="136">
-        <v>15600</v>
-      </c>
-      <c r="E19" s="137">
-        <v>0.77083333333333337</v>
-      </c>
-      <c r="F19" s="137">
-        <v>0.79861111111111116</v>
-      </c>
-      <c r="G19" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" s="136" t="s">
-        <v>62</v>
-      </c>
-      <c r="I19" s="136" t="s">
-        <v>938</v>
-      </c>
-      <c r="J19" s="136"/>
-      <c r="K19" s="136" t="s">
-        <v>92</v>
-      </c>
-      <c r="L19" s="164"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="251"/>
-      <c r="B20" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C20" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="136">
-        <v>19006</v>
-      </c>
-      <c r="E20" s="137">
-        <v>0.8125</v>
-      </c>
-      <c r="F20" s="137">
-        <v>0.84166666666666667</v>
-      </c>
-      <c r="G20" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="H20" s="136" t="s">
-        <v>57</v>
-      </c>
-      <c r="I20" s="136" t="s">
-        <v>112</v>
-      </c>
-      <c r="J20" s="136" t="s">
-        <v>1501</v>
-      </c>
-      <c r="K20" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="L20" s="164"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="251"/>
-      <c r="B21" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C21" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" s="136">
-        <v>19008</v>
-      </c>
-      <c r="E21" s="137">
-        <v>0.8125</v>
-      </c>
-      <c r="F21" s="137">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="G21" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="136" t="s">
-        <v>57</v>
-      </c>
-      <c r="I21" s="136" t="s">
-        <v>746</v>
-      </c>
-      <c r="J21" s="136" t="s">
-        <v>976</v>
-      </c>
-      <c r="K21" s="136" t="s">
-        <v>96</v>
-      </c>
-      <c r="L21" s="164"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="252"/>
-      <c r="B22" s="135">
-        <v>45897</v>
-      </c>
-      <c r="C22" s="136" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="136">
-        <v>19016</v>
-      </c>
-      <c r="E22" s="137">
-        <v>0.84722222222222221</v>
-      </c>
-      <c r="F22" s="137">
-        <v>0.87847222222222221</v>
-      </c>
-      <c r="G22" s="136" t="s">
-        <v>59</v>
-      </c>
-      <c r="H22" s="136" t="s">
-        <v>57</v>
-      </c>
-      <c r="I22" s="136" t="s">
-        <v>1424</v>
-      </c>
-      <c r="J22" s="136" t="s">
-        <v>774</v>
-      </c>
-      <c r="K22" s="136" t="s">
-        <v>89</v>
-      </c>
-      <c r="L22" s="164"/>
+      <c r="L22" s="162"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="157"/>
@@ -23058,7 +23068,7 @@
       <c r="K24" s="136"/>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="241" t="s">
+      <c r="A28" s="163" t="s">
         <v>1575</v>
       </c>
       <c r="B28" s="159">
@@ -23093,7 +23103,7 @@
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="242"/>
+      <c r="A29" s="164"/>
       <c r="B29" s="159">
         <v>45873</v>
       </c>
@@ -23126,7 +23136,7 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="242"/>
+      <c r="A30" s="164"/>
       <c r="B30" s="159">
         <v>45873</v>
       </c>
@@ -23159,7 +23169,7 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="242"/>
+      <c r="A31" s="164"/>
       <c r="B31" s="159">
         <v>45873</v>
       </c>
@@ -23192,7 +23202,7 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="242"/>
+      <c r="A32" s="164"/>
       <c r="B32" s="159">
         <v>45873</v>
       </c>
@@ -23225,7 +23235,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="242"/>
+      <c r="A33" s="164"/>
       <c r="B33" s="159">
         <v>45873</v>
       </c>
@@ -23258,7 +23268,7 @@
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="242"/>
+      <c r="A34" s="164"/>
       <c r="B34" s="159">
         <v>45873</v>
       </c>
@@ -23291,7 +23301,7 @@
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="242"/>
+      <c r="A35" s="164"/>
       <c r="B35" s="159">
         <v>45873</v>
       </c>
@@ -23324,7 +23334,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="242"/>
+      <c r="A36" s="164"/>
       <c r="B36" s="159">
         <v>45873</v>
       </c>
@@ -23357,7 +23367,7 @@
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="242"/>
+      <c r="A37" s="164"/>
       <c r="B37" s="159">
         <v>45873</v>
       </c>
@@ -23390,7 +23400,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="242"/>
+      <c r="A38" s="164"/>
       <c r="B38" s="159">
         <v>45873</v>
       </c>
@@ -23423,7 +23433,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="242"/>
+      <c r="A39" s="164"/>
       <c r="B39" s="159">
         <v>45873</v>
       </c>
@@ -23456,7 +23466,7 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="242"/>
+      <c r="A40" s="164"/>
       <c r="B40" s="159">
         <v>45873</v>
       </c>
@@ -23489,7 +23499,7 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="242"/>
+      <c r="A41" s="164"/>
       <c r="B41" s="159">
         <v>45873</v>
       </c>
@@ -23522,7 +23532,7 @@
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="242"/>
+      <c r="A42" s="164"/>
       <c r="B42" s="159">
         <v>45873</v>
       </c>
@@ -23555,7 +23565,7 @@
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="242"/>
+      <c r="A43" s="164"/>
       <c r="B43" s="159">
         <v>45873</v>
       </c>
@@ -23588,7 +23598,7 @@
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="242"/>
+      <c r="A44" s="164"/>
       <c r="B44" s="159">
         <v>45873</v>
       </c>
@@ -23621,7 +23631,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="242"/>
+      <c r="A45" s="164"/>
       <c r="B45" s="159">
         <v>45873</v>
       </c>
@@ -23654,7 +23664,7 @@
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="242"/>
+      <c r="A46" s="164"/>
       <c r="B46" s="159">
         <v>45873</v>
       </c>
@@ -23687,7 +23697,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="242"/>
+      <c r="A47" s="164"/>
       <c r="B47" s="159">
         <v>45873</v>
       </c>
@@ -23720,7 +23730,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="243"/>
+      <c r="A48" s="165"/>
       <c r="B48" s="159">
         <v>45873</v>
       </c>
@@ -23889,7 +23899,7 @@
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="54">
         <f>escala_do_fluxo[[#This Row],[DATA]]</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B2" s="55">
         <f>'ESCALA RODOVIÁRIA'!B6</f>
@@ -23901,7 +23911,7 @@
       </c>
       <c r="D2" s="55">
         <f>'ESCALA RODOVIÁRIA'!G6</f>
-        <v>25011</v>
+        <v>25007</v>
       </c>
       <c r="E2" s="33" t="str" cm="1">
         <f t="array" ref="E2">_xlfn.XLOOKUP(D2,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1)</f>
@@ -23909,19 +23919,19 @@
       </c>
       <c r="F2" s="56" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D6,"-")),"CANCELADO")</f>
-        <v>JOSE ANTONIO INACIO VIEIRA</v>
+        <v>CLODOALDO PEREIRA DE LIMA</v>
       </c>
       <c r="G2" s="57" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D6,"-"))</f>
-        <v>5279</v>
+        <v>4067</v>
       </c>
       <c r="H2" s="55" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!E6, "-")),"CANCELADO")</f>
-        <v>MARCELO RIZO SANTANA</v>
-      </c>
-      <c r="I2" s="55" t="str">
+        <v>CANCELADO</v>
+      </c>
+      <c r="I2" s="55" t="e">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!E6,"-"))</f>
-        <v>2048</v>
+        <v>#N/A</v>
       </c>
       <c r="J2" s="55" t="str">
         <f>_xlfn.CONCAT('ESCALA RODOVIÁRIA'!H6, " ",TEXT(C2,"HH:MM"))</f>
@@ -23932,7 +23942,7 @@
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="54">
         <f>A2</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B3" s="55">
         <f>'ESCALA RODOVIÁRIA'!B7</f>
@@ -23944,27 +23954,27 @@
       </c>
       <c r="D3" s="55">
         <f>'ESCALA RODOVIÁRIA'!G7</f>
-        <v>24001</v>
+        <v>25011</v>
       </c>
       <c r="E3" s="33" t="str" cm="1">
         <f t="array" ref="E3">_xlfn.XLOOKUP(D3,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1)</f>
-        <v>SD02J77</v>
+        <v>OGT8A57</v>
       </c>
       <c r="F3" s="56" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D7,"-")),"CANCELADO")</f>
-        <v>VALDIR ALVES MIRANDA</v>
+        <v>MARCOS ATAIDE SILVA</v>
       </c>
       <c r="G3" s="57" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D7,"-"))</f>
-        <v>1364</v>
+        <v>1352</v>
       </c>
       <c r="H3" s="55" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!E7, "-")),"CANCELADO")</f>
-        <v>MANOEL SEVERINO DE SOUZA</v>
+        <v>FABIO MOREIRA DOS SANTOS</v>
       </c>
       <c r="I3" s="55" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!E7,"-"))</f>
-        <v>5200</v>
+        <v>3073</v>
       </c>
       <c r="J3" s="55" t="str">
         <f>_xlfn.CONCAT('ESCALA RODOVIÁRIA'!H7, " ",TEXT(C3,"HH:MM"))</f>
@@ -23975,11 +23985,11 @@
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="54">
         <f>A7</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B4" s="55">
         <f>'ESCALA RODOVIÁRIA'!B8</f>
-        <v>4077</v>
+        <v>3132</v>
       </c>
       <c r="C4" s="56">
         <f>'ESCALA RODOVIÁRIA'!C8</f>
@@ -23987,38 +23997,38 @@
       </c>
       <c r="D4" s="55">
         <f>'ESCALA RODOVIÁRIA'!G8</f>
-        <v>19018</v>
+        <v>19005</v>
       </c>
       <c r="E4" s="33" t="str" cm="1">
         <f t="array" ref="E4">_xlfn.XLOOKUP(D4,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1)</f>
-        <v>QTS0454</v>
+        <v>QTQ4724</v>
       </c>
       <c r="F4" s="56" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D8,"-")),"CANCELADO")</f>
-        <v>MARCUS AUGUSTO DE CARVALHO</v>
+        <v>JOSE CARLOS BEZERRA DA SILVA</v>
       </c>
       <c r="G4" s="57" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D8,"-"))</f>
-        <v>2398</v>
+        <v>3034</v>
       </c>
       <c r="H4" s="55" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!E8, "-")),"CANCELADO")</f>
-        <v>LUIS CARLOS VIEIRA DE MELO SOUZA</v>
-      </c>
-      <c r="I4" s="55" t="str">
+        <v>CANCELADO</v>
+      </c>
+      <c r="I4" s="55" t="e">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!E8,"-"))</f>
-        <v>5535</v>
+        <v>#N/A</v>
       </c>
       <c r="J4" s="55" t="str">
         <f>_xlfn.CONCAT('ESCALA RODOVIÁRIA'!H8, " ",TEXT(C4,"HH:MM"))</f>
-        <v>THE X GYN 09:30</v>
+        <v>IMP X PXT 09:30</v>
       </c>
       <c r="K4" s="51"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="58">
         <f>A8</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B5" s="59">
         <f>'ESCALA RODOVIÁRIA'!B57</f>
@@ -24061,7 +24071,7 @@
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="54">
         <f>A3</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B6" s="55">
         <f>'ESCALA RODOVIÁRIA'!B17</f>
@@ -24073,27 +24083,27 @@
       </c>
       <c r="D6" s="55">
         <f>'ESCALA RODOVIÁRIA'!G17</f>
-        <v>19003</v>
+        <v>19007</v>
       </c>
       <c r="E6" s="33" t="str" cm="1">
         <f t="array" ref="E6">_xlfn.XLOOKUP(D6,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1)</f>
-        <v>QTQ8294</v>
+        <v>QTP0317</v>
       </c>
       <c r="F6" s="56" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D17,"-")),"CANCELADO")</f>
-        <v>RONNE RODRIGUES DE SOUSA</v>
+        <v>EDUARDO SANTOS BEZERRA</v>
       </c>
       <c r="G6" s="57" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D17,"-"))</f>
-        <v>5025</v>
+        <v>4066</v>
       </c>
       <c r="H6" s="55" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D18, "-")),"CANCELADO")</f>
-        <v>MARCOS AUGUSTO SILVA ROCHA</v>
-      </c>
-      <c r="I6" s="55" t="str">
+        <v>CANCELADO</v>
+      </c>
+      <c r="I6" s="55" t="e">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D18,"-"))</f>
-        <v>5268</v>
+        <v>#N/A</v>
       </c>
       <c r="J6" s="55" t="str">
         <f>_xlfn.CONCAT('ESCALA RODOVIÁRIA'!H17, " ",TEXT(C6,"HH:MM"))</f>
@@ -24104,7 +24114,7 @@
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="54">
         <f>A6</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B7" s="55">
         <f>'ESCALA RODOVIÁRIA'!B27</f>
@@ -24116,27 +24126,27 @@
       </c>
       <c r="D7" s="55">
         <f>'ESCALA RODOVIÁRIA'!G27</f>
-        <v>19023</v>
+        <v>19021</v>
       </c>
       <c r="E7" s="33" t="str" cm="1">
         <f t="array" ref="E7">_xlfn.XLOOKUP(D7,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1)</f>
-        <v>QTP1I89</v>
+        <v>QTR5657</v>
       </c>
       <c r="F7" s="56" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D27, "-")),"CANCELADO")</f>
-        <v>JOAO DE JESUS GOUVEIA</v>
+        <v>FERNANDO ALVES DE SOUZA</v>
       </c>
       <c r="G7" s="61" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D27,"-"))</f>
-        <v>6016</v>
+        <v>6350</v>
       </c>
       <c r="H7" s="55" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!E27, "-")),"CANCELADO")</f>
-        <v>CLODOALDO PEREIRA DE LIMA</v>
+        <v>AELSON PEREIRA DO NASCIMENTO</v>
       </c>
       <c r="I7" s="55" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!E27,"-"))</f>
-        <v>4067</v>
+        <v>5682</v>
       </c>
       <c r="J7" s="55" t="str">
         <f>_xlfn.CONCAT('ESCALA RODOVIÁRIA'!H27, " ",TEXT(C7,"HH:MM"))</f>
@@ -24147,7 +24157,7 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="54">
         <f>A4</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B8" s="55">
         <f>'ESCALA RODOVIÁRIA'!B39</f>
@@ -24159,27 +24169,27 @@
       </c>
       <c r="D8" s="55">
         <f>'ESCALA RODOVIÁRIA'!G39</f>
-        <v>19013</v>
+        <v>19024</v>
       </c>
       <c r="E8" s="33" t="str" cm="1">
         <f t="array" ref="E8">_xlfn.XLOOKUP(D8,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1)</f>
-        <v>QTR8894</v>
+        <v>QTP1769</v>
       </c>
       <c r="F8" s="56" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D39, "-")),"CANCELADO")</f>
-        <v>KLEBER OLIVEIRA LIMA</v>
+        <v>FRANCISCO BATISTA DE LIMA</v>
       </c>
       <c r="G8" s="61" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D39,"-"))</f>
-        <v>5849</v>
+        <v>1827</v>
       </c>
       <c r="H8" s="55" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D40, "-")),"CANCELADO")</f>
-        <v>LAUCEANDO DA SILVA ROCHA</v>
+        <v>EDIVALDO DE ARAUJO</v>
       </c>
       <c r="I8" s="55" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D40,"-"))</f>
-        <v>6220</v>
+        <v>6217</v>
       </c>
       <c r="J8" s="55" t="str">
         <f>_xlfn.CONCAT('ESCALA RODOVIÁRIA'!H39, " ",TEXT(C8,"HH:MM"))</f>
@@ -24284,7 +24294,7 @@
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <f>A3</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B2" s="12">
         <f>'ESCALA RODOVIÁRIA'!C41</f>
@@ -24294,21 +24304,21 @@
         <f>'ESCALA RODOVIÁRIA'!B41</f>
         <v>4098</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="11">
         <f>'ESCALA RODOVIÁRIA'!G41</f>
-        <v>CANCELADO</v>
+        <v>18016</v>
       </c>
       <c r="E2" s="11" t="str" cm="1">
         <f t="array" ref="E2">IF(D2="CANCELADO","N/A",_xlfn.XLOOKUP(D2,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>N/A</v>
+        <v>PRK6658</v>
       </c>
       <c r="F2" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D41,"-")),"CANCELADO")</f>
-        <v>CANCELADO</v>
+        <v>REGINALDO DE SOUSA OLIVEIRA</v>
       </c>
       <c r="G2" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D41,"-")),"N/A")</f>
-        <v>N/A</v>
+        <v>5412</v>
       </c>
       <c r="H2" s="11" t="s">
         <v>166</v>
@@ -24325,7 +24335,7 @@
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <f>escala_do_fluxo[[#This Row],[DATA]]</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B3" s="12">
         <f>'ESCALA RODOVIÁRIA'!C21</f>
@@ -24333,23 +24343,23 @@
       </c>
       <c r="C3" s="11">
         <f ca="1">IF(TEXT(TODAY(),"DDDD")="SEXTA-FEIRA",9064,4076)</f>
-        <v>4076</v>
+        <v>9064</v>
       </c>
       <c r="D3" s="11">
         <f>'ESCALA RODOVIÁRIA'!G21</f>
-        <v>15600</v>
+        <v>19015</v>
       </c>
       <c r="E3" s="11" t="str" cm="1">
         <f t="array" ref="E3">IF(D3="CANCELADO","N/A",_xlfn.XLOOKUP(D3,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>OOC4709</v>
+        <v>QTS1804</v>
       </c>
       <c r="F3" s="11" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D21,"-")),"CANCELADO")</f>
-        <v>JERZUALDO DA SILVA GOMES</v>
+        <v>FRANCISCO ALVES DA PAZ JUNIOR</v>
       </c>
       <c r="G3" s="12" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D21,"-"))</f>
-        <v>4077</v>
+        <v>1247</v>
       </c>
       <c r="H3" s="11" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!F21,"-")),"CANCELADO")</f>
@@ -24361,7 +24371,7 @@
       </c>
       <c r="J3" s="11" t="str">
         <f>IF(TEXT(A3,"DDDD")="SEXTA-FEIRA","IMP X THE 19:00","GYN X THE 19:00")</f>
-        <v>GYN X THE 19:00</v>
+        <v>IMP X THE 19:00</v>
       </c>
       <c r="K3" s="51"/>
       <c r="N3" s="14" t="s">
@@ -24380,7 +24390,7 @@
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <f>A2</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B4" s="12">
         <v>0.82777777777777783</v>
@@ -24391,27 +24401,27 @@
       </c>
       <c r="D4" s="11">
         <f>'ESCALA RODOVIÁRIA'!G29</f>
-        <v>24005</v>
+        <v>25012</v>
       </c>
       <c r="E4" s="11" t="str" cm="1">
         <f t="array" ref="E4">IF(D4="CANCELADO","N/A",_xlfn.XLOOKUP(D4,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>SDN7G87</v>
+        <v>OGT8A57</v>
       </c>
       <c r="F4" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D29,"-")),"CANCELADO")</f>
-        <v>FRANCISCO BATISTA DE LIMA</v>
+        <v>BRUNO MATOS DA ROCHA</v>
       </c>
       <c r="G4" s="13" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D29,"-"))</f>
-        <v>1827</v>
+        <v>6013</v>
       </c>
       <c r="H4" s="11" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!E29,"-")),"CANCELADO")</f>
-        <v>ADEMILTON DE OLIVEIRA SILVA</v>
+        <v>ANTONIO FRANCINALDO DE OLIVEIRA MARQUES</v>
       </c>
       <c r="I4" s="11" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!E29,"-"))</f>
-        <v>5559</v>
+        <v>5018</v>
       </c>
       <c r="J4" s="11" t="str">
         <f>_xlfn.CONCAT("GYN X BEL ",TEXT(B4,"HH:MM"))</f>
@@ -24432,7 +24442,7 @@
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <f>A4</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B5" s="12">
         <f>'ESCALA RODOVIÁRIA'!C11</f>
@@ -24441,29 +24451,29 @@
       <c r="C5" s="11">
         <v>2261</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="13" t="str">
         <f>'ESCALA RODOVIÁRIA'!G11</f>
-        <v>19006</v>
+        <v>CANCELADO</v>
       </c>
       <c r="E5" s="11" t="str" cm="1">
         <f t="array" ref="E5">IF(D5="CANCELADO","N/A",_xlfn.XLOOKUP(D5,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTO8637</v>
+        <v>N/A</v>
       </c>
       <c r="F5" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D11,"-")),"CANCELADO")</f>
-        <v>MARCIO DE SOUSA MATOS</v>
-      </c>
-      <c r="G5" s="13" t="str">
+        <v>CANCELADO</v>
+      </c>
+      <c r="G5" s="13" t="e">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D11,"-"))</f>
-        <v>5264</v>
+        <v>#N/A</v>
       </c>
       <c r="H5" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!E11,"-")),"CANCELADO")</f>
-        <v>NILSON CORTEZ MIRANDA</v>
-      </c>
-      <c r="I5" s="13" t="str">
+        <v>CANCELADO</v>
+      </c>
+      <c r="I5" s="13" t="e">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!E11,"-"))</f>
-        <v>5636</v>
+        <v>#N/A</v>
       </c>
       <c r="J5" s="11" t="str">
         <f>_xlfn.CONCAT("SLZ X GYN ",TEXT(B5,"HH:MM"))</f>
@@ -24480,7 +24490,7 @@
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <f>A5</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B6" s="12">
         <f>'ESCALA RODOVIÁRIA'!C43</f>
@@ -24491,19 +24501,19 @@
       </c>
       <c r="D6" s="34">
         <f>'ESCALA RODOVIÁRIA'!G43</f>
-        <v>24004</v>
+        <v>25008</v>
       </c>
       <c r="E6" s="11" t="str" cm="1">
         <f t="array" ref="E6">IF(D6="CANCELADO","N/A",_xlfn.XLOOKUP(D6,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>SDJ8I27</v>
+        <v>OGT8A57</v>
       </c>
       <c r="F6" s="11" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D43,"-")),"CANCELADO")</f>
-        <v>ANTONIO MARQUES NETO DOS SANTOS</v>
+        <v>JARDEL DE SOUSA OLIVEIRA</v>
       </c>
       <c r="G6" s="11" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D43,"-"))</f>
-        <v>1738</v>
+        <v>5992</v>
       </c>
       <c r="H6" s="11" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!F43,"-")),"CANCELADO")</f>
@@ -24526,7 +24536,7 @@
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <f>A6</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B7" s="12">
         <f>'ESCALA RODOVIÁRIA'!C12</f>
@@ -24537,27 +24547,27 @@
       </c>
       <c r="D7" s="11">
         <f>'ESCALA RODOVIÁRIA'!G12</f>
-        <v>19008</v>
+        <v>19014</v>
       </c>
       <c r="E7" s="11" t="str" cm="1">
         <f t="array" ref="E7">IF(D7="CANCELADO","N/A",_xlfn.XLOOKUP(D7,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTS0484</v>
+        <v>QTS1814</v>
       </c>
       <c r="F7" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D12,"-")),"CANCELADO")</f>
-        <v>MERVAL DE SOUSA</v>
+        <v>KLEBER OLIVEIRA LIMA</v>
       </c>
       <c r="G7" s="13" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D12,"-"))</f>
-        <v>2880</v>
+        <v>5849</v>
       </c>
       <c r="H7" s="11" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!E12,"-")),"CANCELADO")</f>
-        <v>JOSE ALVES DE FREITAS NETO</v>
-      </c>
-      <c r="I7" s="13" t="str">
+        <v>CANCELADO</v>
+      </c>
+      <c r="I7" s="13" t="e">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!E12,"-"))</f>
-        <v>5027</v>
+        <v>#N/A</v>
       </c>
       <c r="J7" s="11" t="str">
         <f>_xlfn.CONCAT("FOT X SIN ",TEXT(B7,"HH:MM"))</f>
@@ -24568,7 +24578,7 @@
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <f t="shared" ref="A8" si="0">A7</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="B8" s="12">
         <f>'ESCALA RODOVIÁRIA'!C13</f>
@@ -24579,27 +24589,27 @@
       </c>
       <c r="D8" s="11">
         <f>'ESCALA RODOVIÁRIA'!G13</f>
-        <v>19016</v>
+        <v>19010</v>
       </c>
       <c r="E8" s="11" t="str" cm="1">
         <f t="array" ref="E8">IF(D8="CANCELADO","N/A",_xlfn.XLOOKUP(D8,Tabela6[[#All],[Veículo]],Tabela6[[#All],[Placa]],"N/E",1,1))</f>
-        <v>QTS0D94</v>
+        <v>QTO8077</v>
       </c>
       <c r="F8" s="12" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!D13,"-")),"CANCELADO")</f>
-        <v>RAFAEL JOSE TOME DE LIMA</v>
+        <v>MARCIO DE SOUSA MATOS</v>
       </c>
       <c r="G8" s="13" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!D13,"-"))</f>
-        <v>5537</v>
+        <v>5264</v>
       </c>
       <c r="H8" s="11" t="str">
         <f>IFERROR(TRIM(_xlfn.TEXTBEFORE('ESCALA RODOVIÁRIA'!E13,"-")),"CANCELADO")</f>
-        <v>JOAO DA SILVA MORAIS</v>
+        <v>ANDSON WAGNER NASCIMENTO SOUZA</v>
       </c>
       <c r="I8" s="11" t="str">
         <f>TRIM(_xlfn.TEXTAFTER('ESCALA RODOVIÁRIA'!E13,"-"))</f>
-        <v>2978</v>
+        <v>2902</v>
       </c>
       <c r="J8" s="11" t="str">
         <f>_xlfn.CONCAT("BEL X GYN ",TEXT(B8,"HH:MM"))</f>
@@ -24714,7 +24724,7 @@
       <c r="B4" s="80"/>
       <c r="C4" s="87" cm="1">
         <f t="array" aca="1" ref="C4:G10" ca="1">'FROTA NOTURNA'!A2:E8</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="D4" s="88">
         <f ca="1"/>
@@ -24724,20 +24734,20 @@
         <f ca="1"/>
         <v>4098</v>
       </c>
-      <c r="F4" s="89" t="str">
+      <c r="F4" s="89">
         <f ca="1"/>
-        <v>CANCELADO</v>
+        <v>18016</v>
       </c>
       <c r="G4" s="89" t="str">
         <f ca="1"/>
-        <v>N/A</v>
-      </c>
-      <c r="H4" s="244" t="str">
+        <v>PRK6658</v>
+      </c>
+      <c r="H4" s="242" t="str">
         <f>'FROTA NOTURNA'!F2</f>
-        <v>CANCELADO</v>
-      </c>
-      <c r="I4" s="245"/>
-      <c r="J4" s="246"/>
+        <v>REGINALDO DE SOUSA OLIVEIRA</v>
+      </c>
+      <c r="I4" s="243"/>
+      <c r="J4" s="244"/>
       <c r="K4" s="89"/>
       <c r="L4" s="89" t="str" cm="1">
         <f t="array" ref="L4:L10">'FROTA NOTURNA'!J2:J8</f>
@@ -24752,7 +24762,7 @@
       <c r="B5" s="80"/>
       <c r="C5" s="87">
         <f ca="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="D5" s="88">
         <f ca="1"/>
@@ -24760,25 +24770,25 @@
       </c>
       <c r="E5" s="89">
         <f ca="1"/>
-        <v>4076</v>
+        <v>9064</v>
       </c>
       <c r="F5" s="89">
         <f ca="1"/>
-        <v>15600</v>
+        <v>19015</v>
       </c>
       <c r="G5" s="89" t="str">
         <f ca="1"/>
-        <v>OOC4709</v>
-      </c>
-      <c r="H5" s="247" t="str">
+        <v>QTS1804</v>
+      </c>
+      <c r="H5" s="245" t="str">
         <f>'FROTA NOTURNA'!F3</f>
-        <v>JERZUALDO DA SILVA GOMES</v>
-      </c>
-      <c r="I5" s="248"/>
-      <c r="J5" s="249"/>
+        <v>FRANCISCO ALVES DA PAZ JUNIOR</v>
+      </c>
+      <c r="I5" s="246"/>
+      <c r="J5" s="247"/>
       <c r="K5" s="89"/>
       <c r="L5" s="89" t="str">
-        <v>GYN X THE 19:00</v>
+        <v>IMP X THE 19:00</v>
       </c>
       <c r="M5" s="91"/>
       <c r="N5" s="81"/>
@@ -24787,7 +24797,7 @@
       <c r="B6" s="80"/>
       <c r="C6" s="87">
         <f ca="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="D6" s="88">
         <f ca="1"/>
@@ -24799,20 +24809,20 @@
       </c>
       <c r="F6" s="89">
         <f ca="1"/>
-        <v>24005</v>
+        <v>25012</v>
       </c>
       <c r="G6" s="89" t="str">
         <f ca="1"/>
-        <v>SDN7G87</v>
+        <v>OGT8A57</v>
       </c>
       <c r="H6" s="88" t="str">
         <f>'FROTA NOTURNA'!F4</f>
-        <v>FRANCISCO BATISTA DE LIMA</v>
+        <v>BRUNO MATOS DA ROCHA</v>
       </c>
       <c r="I6" s="92"/>
       <c r="J6" s="88" t="str">
         <f>'FROTA NOTURNA'!H4</f>
-        <v>ADEMILTON DE OLIVEIRA SILVA</v>
+        <v>ANTONIO FRANCINALDO DE OLIVEIRA MARQUES</v>
       </c>
       <c r="K6" s="89"/>
       <c r="L6" s="89" t="str">
@@ -24825,7 +24835,7 @@
       <c r="B7" s="80"/>
       <c r="C7" s="87">
         <f ca="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="D7" s="88">
         <f ca="1"/>
@@ -24835,22 +24845,22 @@
         <f ca="1"/>
         <v>2261</v>
       </c>
-      <c r="F7" s="92">
+      <c r="F7" s="92" t="str">
         <f ca="1"/>
-        <v>19006</v>
+        <v>CANCELADO</v>
       </c>
       <c r="G7" s="89" t="str">
         <f ca="1"/>
-        <v>QTO8637</v>
+        <v>N/A</v>
       </c>
       <c r="H7" s="88" t="str">
         <f>'FROTA NOTURNA'!F5</f>
-        <v>MARCIO DE SOUSA MATOS</v>
+        <v>CANCELADO</v>
       </c>
       <c r="I7" s="92"/>
       <c r="J7" s="89" t="str">
         <f>'FROTA NOTURNA'!H5</f>
-        <v>NILSON CORTEZ MIRANDA</v>
+        <v>CANCELADO</v>
       </c>
       <c r="K7" s="92"/>
       <c r="L7" s="89" t="str">
@@ -24863,7 +24873,7 @@
       <c r="B8" s="80"/>
       <c r="C8" s="87">
         <f ca="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="D8" s="88">
         <f ca="1"/>
@@ -24875,18 +24885,18 @@
       </c>
       <c r="F8" s="93">
         <f ca="1"/>
-        <v>24004</v>
+        <v>25008</v>
       </c>
       <c r="G8" s="89" t="str">
         <f ca="1"/>
-        <v>SDJ8I27</v>
-      </c>
-      <c r="H8" s="247" t="str">
+        <v>OGT8A57</v>
+      </c>
+      <c r="H8" s="245" t="str">
         <f>'FROTA NOTURNA'!F6</f>
-        <v>ANTONIO MARQUES NETO DOS SANTOS</v>
-      </c>
-      <c r="I8" s="248"/>
-      <c r="J8" s="249"/>
+        <v>JARDEL DE SOUSA OLIVEIRA</v>
+      </c>
+      <c r="I8" s="246"/>
+      <c r="J8" s="247"/>
       <c r="K8" s="89"/>
       <c r="L8" s="89" t="str">
         <v>GYN X SLZ 20:15</v>
@@ -24898,7 +24908,7 @@
       <c r="B9" s="80"/>
       <c r="C9" s="87">
         <f ca="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="D9" s="88">
         <f ca="1"/>
@@ -24910,20 +24920,20 @@
       </c>
       <c r="F9" s="89">
         <f ca="1"/>
-        <v>19008</v>
+        <v>19014</v>
       </c>
       <c r="G9" s="89" t="str">
         <f ca="1"/>
-        <v>QTS0484</v>
+        <v>QTS1814</v>
       </c>
       <c r="H9" s="88" t="str">
         <f>'FROTA NOTURNA'!F7</f>
-        <v>MERVAL DE SOUSA</v>
+        <v>KLEBER OLIVEIRA LIMA</v>
       </c>
       <c r="I9" s="92"/>
       <c r="J9" s="89" t="str">
         <f>'FROTA NOTURNA'!H7</f>
-        <v>JOSE ALVES DE FREITAS NETO</v>
+        <v>CANCELADO</v>
       </c>
       <c r="K9" s="92"/>
       <c r="L9" s="89" t="str">
@@ -24936,7 +24946,7 @@
       <c r="B10" s="80"/>
       <c r="C10" s="87">
         <f ca="1"/>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="D10" s="88">
         <f ca="1"/>
@@ -24948,20 +24958,20 @@
       </c>
       <c r="F10" s="89">
         <f ca="1"/>
-        <v>19016</v>
+        <v>19010</v>
       </c>
       <c r="G10" s="89" t="str">
         <f ca="1"/>
-        <v>QTS0D94</v>
+        <v>QTO8077</v>
       </c>
       <c r="H10" s="88" t="str">
         <f>'FROTA NOTURNA'!F8</f>
-        <v>RAFAEL JOSE TOME DE LIMA</v>
+        <v>MARCIO DE SOUSA MATOS</v>
       </c>
       <c r="I10" s="92"/>
       <c r="J10" s="89" t="str">
         <f>'FROTA NOTURNA'!H8</f>
-        <v>JOAO DA SILVA MORAIS</v>
+        <v>ANDSON WAGNER NASCIMENTO SOUZA</v>
       </c>
       <c r="K10" s="89"/>
       <c r="L10" s="89" t="str">
@@ -24974,7 +24984,7 @@
       <c r="B11" s="80"/>
       <c r="C11" s="87">
         <f ca="1">C10</f>
-        <v>45897</v>
+        <v>46101</v>
       </c>
       <c r="D11" s="88">
         <f>'FRT NTR BFM'!B14</f>
@@ -25045,7 +25055,7 @@
       <c r="I14" s="83"/>
       <c r="J14" s="155" t="str">
         <f ca="1">_xlfn.CONCAT("última atualização: ", TEXT(NOW(),"hh:mm"))</f>
-        <v>última atualização: 18:49</v>
+        <v>última atualização: 05:36</v>
       </c>
       <c r="K14" s="83"/>
       <c r="L14" s="83"/>
